--- a/InputData/elec/DRCo/Demand Response Costs.xlsx
+++ b/InputData/elec/DRCo/Demand Response Costs.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28507"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rod\Desktop\elec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skorpius/My Drive/2024/FO local_EPS ICM/Diario/20250507_FINAL/DRCo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{66CD638D-E5A2-4D20-A93E-2AA87FF17ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F2ABAD3-FA69-4DAF-97B5-D8BE1AFB3769}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5739A9D9-7F1D-9642-9F71-266B30BFE332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2500" yWindow="-21100" windowWidth="29520" windowHeight="20500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="4" r:id="rId1"/>
     <sheet name="Demand Response_States" sheetId="1" r:id="rId2"/>
-    <sheet name="Calculations" sheetId="6" r:id="rId3"/>
-    <sheet name="DRCo-ACpUDRC" sheetId="5" r:id="rId4"/>
-    <sheet name="DRCo-SoDRbP" sheetId="7" r:id="rId5"/>
+    <sheet name="Mexico_id-7" sheetId="8" r:id="rId3"/>
+    <sheet name="PreciosServiciosConexos SIN MTR" sheetId="9" r:id="rId4"/>
+    <sheet name="Calculations" sheetId="6" r:id="rId5"/>
+    <sheet name="DRCo-ACpUDRC" sheetId="5" r:id="rId6"/>
+    <sheet name="DRCo-SoDRbP" sheetId="7" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Demand Response_States'!$A$3:$AN$430</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Demand Response_States'!$1:$3</definedName>
@@ -46,30 +45,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7365" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7736" uniqueCount="645">
   <si>
     <t>DRCo Annual Cost per Unit Demand Response Capacity</t>
   </si>
@@ -1743,6 +1720,267 @@
   </si>
   <si>
     <t>share</t>
+  </si>
+  <si>
+    <t>Fuente: Sistema de Información Energética (SIE) con información del Balance Nacional de Energía, SENER.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   La suma de los parciales puede no coincidir con los totales debido al redondeo de las cifras.</t>
+  </si>
+  <si>
+    <t>Nota:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Energía eléctrica</t>
+  </si>
+  <si>
+    <t>Público</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Gas seco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Diesel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Gas licuado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Total de petrolíferos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Energía solar</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Querosenos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Leña</t>
+  </si>
+  <si>
+    <t>Residencial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Diesel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Querosenos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Gas licuado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Total petrolíferos</t>
+  </si>
+  <si>
+    <t>Total sector residencial, comercial y público</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>(petajoules)</t>
+  </si>
+  <si>
+    <t>Balance Nacional de Energía: Consumo de energía en los sectores residencial, comercial y público</t>
+  </si>
+  <si>
+    <t>Dirección General de Planeación e Información  Energéticas</t>
+  </si>
+  <si>
+    <t>Secretaría de Energía</t>
+  </si>
+  <si>
+    <t>Sistema de Información Energética</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   A partir del 2021 se considera la clasificación industrial del Sistema de Clasificación Industrial de América del Norte (SCIAN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   A partir de 2021 se consideran los permisos de generación eléctrica de pequenos productores, cogeneración y usos propios continuos. Del mismo modo, las centrales públicas se denominan Centrales Eléctricas de CFE</t>
+  </si>
+  <si>
+    <t>Notas:</t>
+  </si>
+  <si>
+    <t>N/D</t>
+  </si>
+  <si>
+    <t>Dirección General de Planeación e Información Energéticas</t>
+  </si>
+  <si>
+    <t>Fuente: Sistema de Información Energética, SENER.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   A partir de 2021 se consideran perdidas no técnicas, porteo y suministro calificado de energía eléctrica.</t>
+  </si>
+  <si>
+    <t>Electricidad</t>
+  </si>
+  <si>
+    <t>Fabricación de fertilizantes</t>
+  </si>
+  <si>
+    <t>Elaboración de refrescos, hielo y otras bebidas no alcohólicas, purificación y embotellado de agua</t>
+  </si>
+  <si>
+    <t>Elaboración de cerveza</t>
+  </si>
+  <si>
+    <t>Fabricación de vidrio y productos de vidrio</t>
+  </si>
+  <si>
+    <t>Otras ramas</t>
+  </si>
+  <si>
+    <t>Pemex Petroquímica</t>
+  </si>
+  <si>
+    <t>339.- Otras industrias manufactureras</t>
+  </si>
+  <si>
+    <t>336.-Fabricación de equipo de transporte</t>
+  </si>
+  <si>
+    <t>335.-Fabricación de accesorios, aparatos eléctricos y equipo de generación de energía eléctrica</t>
+  </si>
+  <si>
+    <t>334.-Fabricación de equipo de computación, comunicación, medición y de otros equipos, componentes y accesorios electrónico</t>
+  </si>
+  <si>
+    <t>331.- Industrias metálicas básicas</t>
+  </si>
+  <si>
+    <t>327.-Fabricación de productos a base de minerales no metálicos</t>
+  </si>
+  <si>
+    <t>326.- Industria del plástico y del hule</t>
+  </si>
+  <si>
+    <t>325.- Industria química</t>
+  </si>
+  <si>
+    <t>322.-Industria del papel</t>
+  </si>
+  <si>
+    <t>313.- Fabricación de insumos textiles y acabados textiles</t>
+  </si>
+  <si>
+    <t>Energía Eléctrica</t>
+  </si>
+  <si>
+    <t>312.- Industria de las bebidas y del tabaco</t>
+  </si>
+  <si>
+    <t>311.- Industria alimentaria</t>
+  </si>
+  <si>
+    <t>236.- Edificación</t>
+  </si>
+  <si>
+    <t>212.- Minería de minerales metálicos y no metálicos, excepto petróleo y gas</t>
+  </si>
+  <si>
+    <t>Total sector industrial</t>
+  </si>
+  <si>
+    <t>Balance Nacional de Energía: Consumo de energía en el sector industrial</t>
+  </si>
+  <si>
+    <t>Energía eléctrica DR</t>
+  </si>
+  <si>
+    <t>Reserva no rodante suplementarias</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>Reserva rodante suplementaria</t>
+  </si>
+  <si>
+    <t>Reserva no rodante de 10 minutos</t>
+  </si>
+  <si>
+    <t>Reserva rodante de 10 minutos</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Reserva de regulacion secundaria</t>
+  </si>
+  <si>
+    <t>HORA</t>
+  </si>
+  <si>
+    <t>SIN Total</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Average of  Precio de la reserva ($/MW por hora)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Precio de la reserva ($/MW por hora)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tipo de reserva</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Zona de reserva</t>
+  </si>
+  <si>
+    <t>Hora</t>
+  </si>
+  <si>
+    <t>Nota: Los acentos de este reporte se omiten intencionalmente por sistema.</t>
+  </si>
+  <si>
+    <t>Archivo descargado desde el Sistema de Informacion del Mercado (Area Publica) creado el 14/may/2025 16:19:20 hrs</t>
+  </si>
+  <si>
+    <t>Fecha: 11/may/2025</t>
+  </si>
+  <si>
+    <t>Reporte diario</t>
+  </si>
+  <si>
+    <t>Sistema Interconectado Nacional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precios de Servicios Conexos del MTR (Calculo ExPost)					</t>
+  </si>
+  <si>
+    <t>Centro Nacional de Control de Energia</t>
+  </si>
+  <si>
+    <t>2023 to 2012 USD</t>
+  </si>
+  <si>
+    <t>MXN23</t>
+  </si>
+  <si>
+    <t>USD23</t>
+  </si>
+  <si>
+    <t>USD22</t>
+  </si>
+  <si>
+    <t>per year</t>
   </si>
 </sst>
 </file>
@@ -1754,9 +1992,16 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1909,11 +2154,13 @@
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
@@ -1923,8 +2170,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="40">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2146,8 +2412,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -2399,231 +2677,266 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="44">
+  <cellStyleXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="6" borderId="4" xfId="11" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="4" xfId="11" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="6" borderId="4" xfId="11" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="4" xfId="11" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="43"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="43"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="38" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="21" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="38" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="21" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="22" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="21" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="22" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="21" fillId="38" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="22" fillId="38" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="39" borderId="0" xfId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="3" fontId="11" fillId="6" borderId="18" xfId="11" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="39" borderId="0" xfId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="18" xfId="11" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="6" borderId="19" xfId="11" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="19" xfId="11" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="6" borderId="20" xfId="11" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="20" xfId="11" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="44"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="44" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="14" xfId="11" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="11" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="15" xfId="11" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="15" xfId="11" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="11" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="16" xfId="11" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="17" xfId="11" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="17" xfId="11" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="45"/>
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="21" xfId="45" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="21" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="41" borderId="0" xfId="45" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="45" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="41" borderId="22" xfId="45" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="22" xfId="45" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" xfId="45" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" xfId="45" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="44">
+  <cellStyles count="46">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -2662,9 +2975,11 @@
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="44" xr:uid="{B728CD6D-5392-5940-BAFC-DF3D03528902}"/>
+    <cellStyle name="Normal 3" xfId="45" xr:uid="{1F0A90EF-440E-B849-9CC7-C3FA8E3FC5C3}"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Percent" xfId="42" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="42" builtinId="5"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
@@ -2680,21 +2995,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Calculations"/>
-      <sheetName val="About"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2961,22 +3261,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="49.28515625" customWidth="1"/>
+    <col min="2" max="2" width="49.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -2984,122 +3284,122 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" s="6">
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="34">
         <v>0.9143</v>
       </c>
@@ -3119,145 +3419,145 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN432"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" style="35" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="35" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="35" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="35" customWidth="1"/>
-    <col min="10" max="12" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="27" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="32" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="37" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" style="35" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" style="35" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="35" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" style="35" customWidth="1"/>
+    <col min="10" max="12" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="32" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="37" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="30" customHeight="1">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="42"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="15"/>
-      <c r="F1" s="61" t="s">
+      <c r="F1" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="43" t="s">
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
-      <c r="AB1" s="44"/>
-      <c r="AC1" s="45"/>
-      <c r="AD1" s="46" t="s">
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
+      <c r="AB1" s="46"/>
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="47"/>
-      <c r="AH1" s="47"/>
-      <c r="AI1" s="47"/>
-      <c r="AJ1" s="47"/>
-      <c r="AK1" s="47"/>
-      <c r="AL1" s="47"/>
-      <c r="AM1" s="48"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
+      <c r="AL1" s="49"/>
+      <c r="AM1" s="50"/>
       <c r="AN1" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:40" ht="14.25" customHeight="1">
-      <c r="A2" s="40" t="s">
+    <row r="2" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
       <c r="E2" s="15"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="49" t="s">
+      <c r="F2" s="65"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="52" t="s">
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="54"/>
-      <c r="T2" s="49" t="s">
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="52" t="s">
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="53"/>
+      <c r="Y2" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="53"/>
-      <c r="AB2" s="53"/>
-      <c r="AC2" s="54"/>
-      <c r="AD2" s="55" t="s">
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="55"/>
+      <c r="AC2" s="56"/>
+      <c r="AD2" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="AE2" s="56"/>
-      <c r="AF2" s="56"/>
-      <c r="AG2" s="56"/>
-      <c r="AH2" s="57"/>
-      <c r="AI2" s="58" t="s">
+      <c r="AE2" s="58"/>
+      <c r="AF2" s="58"/>
+      <c r="AG2" s="58"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
-      <c r="AM2" s="60"/>
+      <c r="AJ2" s="61"/>
+      <c r="AK2" s="61"/>
+      <c r="AL2" s="61"/>
+      <c r="AM2" s="62"/>
       <c r="AN2" s="16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:40" ht="60">
+    <row r="3" spans="1:40" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
         <v>39</v>
       </c>
@@ -3379,7 +3679,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="31">
         <v>2018</v>
       </c>
@@ -3505,7 +3805,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="31">
         <v>2018</v>
       </c>
@@ -3631,7 +3931,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="31">
         <v>2018</v>
       </c>
@@ -3757,7 +4057,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="31">
         <v>2018</v>
       </c>
@@ -3883,7 +4183,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="31">
         <v>2018</v>
       </c>
@@ -4009,7 +4309,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="31">
         <v>2018</v>
       </c>
@@ -4135,7 +4435,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:40">
+    <row r="10" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="31">
         <v>2018</v>
       </c>
@@ -4261,7 +4561,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="31">
         <v>2018</v>
       </c>
@@ -4387,7 +4687,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="31">
         <v>2018</v>
       </c>
@@ -4513,7 +4813,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:40">
+    <row r="13" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="31">
         <v>2018</v>
       </c>
@@ -4639,7 +4939,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:40">
+    <row r="14" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="31">
         <v>2018</v>
       </c>
@@ -4765,7 +5065,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:40">
+    <row r="15" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="31">
         <v>2018</v>
       </c>
@@ -4891,7 +5191,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:40">
+    <row r="16" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="31">
         <v>2018</v>
       </c>
@@ -5017,7 +5317,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:40">
+    <row r="17" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="31">
         <v>2018</v>
       </c>
@@ -5143,7 +5443,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:40">
+    <row r="18" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="31">
         <v>2018</v>
       </c>
@@ -5269,7 +5569,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:40">
+    <row r="19" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="31">
         <v>2018</v>
       </c>
@@ -5395,7 +5695,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:40">
+    <row r="20" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="31">
         <v>2018</v>
       </c>
@@ -5521,7 +5821,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:40">
+    <row r="21" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="31">
         <v>2018</v>
       </c>
@@ -5647,7 +5947,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:40">
+    <row r="22" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="31">
         <v>2018</v>
       </c>
@@ -5773,7 +6073,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:40">
+    <row r="23" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="31">
         <v>2018</v>
       </c>
@@ -5899,7 +6199,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:40">
+    <row r="24" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="31">
         <v>2018</v>
       </c>
@@ -6025,7 +6325,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="25" spans="1:40">
+    <row r="25" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="31">
         <v>2018</v>
       </c>
@@ -6151,7 +6451,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:40">
+    <row r="26" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="31">
         <v>2018</v>
       </c>
@@ -6277,7 +6577,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:40">
+    <row r="27" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="31">
         <v>2018</v>
       </c>
@@ -6403,7 +6703,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:40">
+    <row r="28" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="31">
         <v>2018</v>
       </c>
@@ -6529,7 +6829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:40">
+    <row r="29" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="31">
         <v>2018</v>
       </c>
@@ -6655,7 +6955,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:40">
+    <row r="30" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="31">
         <v>2018</v>
       </c>
@@ -6781,7 +7081,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="31" spans="1:40">
+    <row r="31" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="31">
         <v>2018</v>
       </c>
@@ -6907,7 +7207,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:40">
+    <row r="32" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="31">
         <v>2018</v>
       </c>
@@ -7033,7 +7333,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:40">
+    <row r="33" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="31">
         <v>2018</v>
       </c>
@@ -7159,7 +7459,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:40">
+    <row r="34" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="31">
         <v>2018</v>
       </c>
@@ -7285,7 +7585,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:40">
+    <row r="35" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="31">
         <v>2018</v>
       </c>
@@ -7411,7 +7711,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:40">
+    <row r="36" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="31">
         <v>2018</v>
       </c>
@@ -7537,7 +7837,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:40">
+    <row r="37" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="31">
         <v>2018</v>
       </c>
@@ -7663,7 +7963,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:40">
+    <row r="38" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="31">
         <v>2018</v>
       </c>
@@ -7789,7 +8089,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:40">
+    <row r="39" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="31">
         <v>2018</v>
       </c>
@@ -7915,7 +8215,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="1:40">
+    <row r="40" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="31">
         <v>2018</v>
       </c>
@@ -8041,7 +8341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:40">
+    <row r="41" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="31">
         <v>2018</v>
       </c>
@@ -8167,7 +8467,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:40">
+    <row r="42" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="31">
         <v>2018</v>
       </c>
@@ -8293,7 +8593,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="1:40">
+    <row r="43" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="31">
         <v>2018</v>
       </c>
@@ -8419,7 +8719,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="1:40">
+    <row r="44" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="31">
         <v>2018</v>
       </c>
@@ -8545,7 +8845,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:40">
+    <row r="45" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="31">
         <v>2018</v>
       </c>
@@ -8671,7 +8971,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:40">
+    <row r="46" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="31">
         <v>2018</v>
       </c>
@@ -8797,7 +9097,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:40">
+    <row r="47" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="31">
         <v>2018</v>
       </c>
@@ -8923,7 +9223,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:40">
+    <row r="48" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="31">
         <v>2018</v>
       </c>
@@ -9049,7 +9349,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="49" spans="1:40">
+    <row r="49" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="31">
         <v>2018</v>
       </c>
@@ -9175,7 +9475,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="1:40">
+    <row r="50" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="31">
         <v>2018</v>
       </c>
@@ -9301,7 +9601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:40">
+    <row r="51" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="31">
         <v>2018</v>
       </c>
@@ -9427,7 +9727,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="1:40">
+    <row r="52" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="31">
         <v>2018</v>
       </c>
@@ -9553,7 +9853,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:40">
+    <row r="53" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="31">
         <v>2018</v>
       </c>
@@ -9679,7 +9979,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:40">
+    <row r="54" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="31">
         <v>2018</v>
       </c>
@@ -9805,7 +10105,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:40">
+    <row r="55" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="31">
         <v>2018</v>
       </c>
@@ -9931,7 +10231,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:40">
+    <row r="56" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="31">
         <v>2018</v>
       </c>
@@ -10057,7 +10357,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="1:40">
+    <row r="57" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="31">
         <v>2018</v>
       </c>
@@ -10183,7 +10483,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:40">
+    <row r="58" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="31">
         <v>2018</v>
       </c>
@@ -10309,7 +10609,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:40">
+    <row r="59" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="31">
         <v>2018</v>
       </c>
@@ -10435,7 +10735,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:40">
+    <row r="60" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="31">
         <v>2018</v>
       </c>
@@ -10561,7 +10861,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="61" spans="1:40">
+    <row r="61" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="31">
         <v>2018</v>
       </c>
@@ -10687,7 +10987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:40">
+    <row r="62" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="31">
         <v>2018</v>
       </c>
@@ -10813,7 +11113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:40">
+    <row r="63" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="31">
         <v>2018</v>
       </c>
@@ -10939,7 +11239,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="1:40">
+    <row r="64" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="31">
         <v>2018</v>
       </c>
@@ -11065,7 +11365,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="65" spans="1:40">
+    <row r="65" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="31">
         <v>2018</v>
       </c>
@@ -11191,7 +11491,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="66" spans="1:40">
+    <row r="66" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="31">
         <v>2018</v>
       </c>
@@ -11317,7 +11617,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="1:40">
+    <row r="67" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="31">
         <v>2018</v>
       </c>
@@ -11443,7 +11743,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="68" spans="1:40">
+    <row r="68" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="31">
         <v>2018</v>
       </c>
@@ -11569,7 +11869,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="69" spans="1:40">
+    <row r="69" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="31">
         <v>2018</v>
       </c>
@@ -11695,7 +11995,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="70" spans="1:40">
+    <row r="70" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="31">
         <v>2018</v>
       </c>
@@ -11821,7 +12121,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="71" spans="1:40">
+    <row r="71" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="31">
         <v>2018</v>
       </c>
@@ -11947,7 +12247,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="72" spans="1:40">
+    <row r="72" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="31">
         <v>2018</v>
       </c>
@@ -12073,7 +12373,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="73" spans="1:40">
+    <row r="73" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="31">
         <v>2018</v>
       </c>
@@ -12199,7 +12499,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="74" spans="1:40">
+    <row r="74" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="31">
         <v>2018</v>
       </c>
@@ -12325,7 +12625,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="75" spans="1:40">
+    <row r="75" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="31">
         <v>2018</v>
       </c>
@@ -12451,7 +12751,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="1:40">
+    <row r="76" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="31">
         <v>2018</v>
       </c>
@@ -12577,7 +12877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:40">
+    <row r="77" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="31">
         <v>2018</v>
       </c>
@@ -12703,7 +13003,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="78" spans="1:40">
+    <row r="78" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="31">
         <v>2018</v>
       </c>
@@ -12829,7 +13129,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="79" spans="1:40">
+    <row r="79" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="31">
         <v>2018</v>
       </c>
@@ -12955,7 +13255,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="80" spans="1:40">
+    <row r="80" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="31">
         <v>2018</v>
       </c>
@@ -13081,7 +13381,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="81" spans="1:40">
+    <row r="81" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="31">
         <v>2018</v>
       </c>
@@ -13207,7 +13507,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="82" spans="1:40">
+    <row r="82" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="31">
         <v>2018</v>
       </c>
@@ -13333,7 +13633,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:40">
+    <row r="83" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="31">
         <v>2018</v>
       </c>
@@ -13459,7 +13759,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="84" spans="1:40">
+    <row r="84" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="31">
         <v>2018</v>
       </c>
@@ -13585,7 +13885,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="85" spans="1:40">
+    <row r="85" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="31">
         <v>2018</v>
       </c>
@@ -13711,7 +14011,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="86" spans="1:40">
+    <row r="86" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="31">
         <v>2018</v>
       </c>
@@ -13837,7 +14137,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="87" spans="1:40">
+    <row r="87" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="31">
         <v>2018</v>
       </c>
@@ -13963,7 +14263,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="88" spans="1:40">
+    <row r="88" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="31">
         <v>2018</v>
       </c>
@@ -14089,7 +14389,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="89" spans="1:40">
+    <row r="89" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="31">
         <v>2018</v>
       </c>
@@ -14215,7 +14515,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="90" spans="1:40">
+    <row r="90" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="31">
         <v>2018</v>
       </c>
@@ -14341,7 +14641,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="91" spans="1:40">
+    <row r="91" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="31">
         <v>2018</v>
       </c>
@@ -14467,7 +14767,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="92" spans="1:40">
+    <row r="92" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="31">
         <v>2018</v>
       </c>
@@ -14593,7 +14893,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="93" spans="1:40">
+    <row r="93" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="31">
         <v>2018</v>
       </c>
@@ -14719,7 +15019,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="94" spans="1:40">
+    <row r="94" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="31">
         <v>2018</v>
       </c>
@@ -14845,7 +15145,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="95" spans="1:40">
+    <row r="95" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="31">
         <v>2018</v>
       </c>
@@ -14971,7 +15271,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="96" spans="1:40">
+    <row r="96" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="31">
         <v>2018</v>
       </c>
@@ -15097,7 +15397,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="97" spans="1:40">
+    <row r="97" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="31">
         <v>2018</v>
       </c>
@@ -15223,7 +15523,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:40">
+    <row r="98" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="31">
         <v>2018</v>
       </c>
@@ -15349,7 +15649,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="99" spans="1:40">
+    <row r="99" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="31">
         <v>2018</v>
       </c>
@@ -15475,7 +15775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:40">
+    <row r="100" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="31">
         <v>2018</v>
       </c>
@@ -15601,7 +15901,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="101" spans="1:40">
+    <row r="101" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="31">
         <v>2018</v>
       </c>
@@ -15727,7 +16027,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="102" spans="1:40">
+    <row r="102" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="31">
         <v>2018</v>
       </c>
@@ -15853,7 +16153,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="103" spans="1:40">
+    <row r="103" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="31">
         <v>2018</v>
       </c>
@@ -15979,7 +16279,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="104" spans="1:40">
+    <row r="104" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="31">
         <v>2018</v>
       </c>
@@ -16105,7 +16405,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="105" spans="1:40">
+    <row r="105" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="31">
         <v>2018</v>
       </c>
@@ -16231,7 +16531,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="106" spans="1:40">
+    <row r="106" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="31">
         <v>2018</v>
       </c>
@@ -16357,7 +16657,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="107" spans="1:40">
+    <row r="107" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="31">
         <v>2018</v>
       </c>
@@ -16483,7 +16783,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="108" spans="1:40">
+    <row r="108" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="31">
         <v>2018</v>
       </c>
@@ -16609,7 +16909,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="109" spans="1:40">
+    <row r="109" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="31">
         <v>2018</v>
       </c>
@@ -16735,7 +17035,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="110" spans="1:40">
+    <row r="110" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="31">
         <v>2018</v>
       </c>
@@ -16861,7 +17161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:40">
+    <row r="111" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="31">
         <v>2018</v>
       </c>
@@ -16987,7 +17287,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="112" spans="1:40">
+    <row r="112" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="31">
         <v>2018</v>
       </c>
@@ -17113,7 +17413,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="113" spans="1:40">
+    <row r="113" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="31">
         <v>2018</v>
       </c>
@@ -17239,7 +17539,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="114" spans="1:40">
+    <row r="114" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="31">
         <v>2018</v>
       </c>
@@ -17365,7 +17665,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="115" spans="1:40">
+    <row r="115" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A115" s="31">
         <v>2018</v>
       </c>
@@ -17491,7 +17791,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="116" spans="1:40">
+    <row r="116" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" s="31">
         <v>2018</v>
       </c>
@@ -17617,7 +17917,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="117" spans="1:40">
+    <row r="117" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="31">
         <v>2018</v>
       </c>
@@ -17743,7 +18043,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="118" spans="1:40">
+    <row r="118" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="31">
         <v>2018</v>
       </c>
@@ -17869,7 +18169,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="119" spans="1:40">
+    <row r="119" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="31">
         <v>2018</v>
       </c>
@@ -17995,7 +18295,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="120" spans="1:40">
+    <row r="120" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" s="31">
         <v>2018</v>
       </c>
@@ -18121,7 +18421,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="121" spans="1:40">
+    <row r="121" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A121" s="31">
         <v>2018</v>
       </c>
@@ -18247,7 +18547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:40">
+    <row r="122" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" s="31">
         <v>2018</v>
       </c>
@@ -18373,7 +18673,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="123" spans="1:40">
+    <row r="123" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" s="31">
         <v>2018</v>
       </c>
@@ -18499,7 +18799,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="124" spans="1:40">
+    <row r="124" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" s="31">
         <v>2018</v>
       </c>
@@ -18625,7 +18925,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="125" spans="1:40">
+    <row r="125" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A125" s="31">
         <v>2018</v>
       </c>
@@ -18751,7 +19051,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="126" spans="1:40">
+    <row r="126" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" s="31">
         <v>2018</v>
       </c>
@@ -18877,7 +19177,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="127" spans="1:40">
+    <row r="127" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" s="31">
         <v>2018</v>
       </c>
@@ -19003,7 +19303,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="128" spans="1:40">
+    <row r="128" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A128" s="31">
         <v>2018</v>
       </c>
@@ -19129,7 +19429,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="129" spans="1:40">
+    <row r="129" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A129" s="31">
         <v>2018</v>
       </c>
@@ -19255,7 +19555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:40">
+    <row r="130" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A130" s="31">
         <v>2018</v>
       </c>
@@ -19381,7 +19681,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="131" spans="1:40">
+    <row r="131" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A131" s="31">
         <v>2018</v>
       </c>
@@ -19507,7 +19807,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="132" spans="1:40">
+    <row r="132" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="31">
         <v>2018</v>
       </c>
@@ -19633,7 +19933,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="133" spans="1:40">
+    <row r="133" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A133" s="31">
         <v>2018</v>
       </c>
@@ -19759,7 +20059,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="134" spans="1:40">
+    <row r="134" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A134" s="31">
         <v>2018</v>
       </c>
@@ -19885,7 +20185,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="135" spans="1:40">
+    <row r="135" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" s="31">
         <v>2018</v>
       </c>
@@ -20011,7 +20311,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="136" spans="1:40">
+    <row r="136" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" s="31">
         <v>2018</v>
       </c>
@@ -20137,7 +20437,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="137" spans="1:40">
+    <row r="137" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A137" s="31">
         <v>2018</v>
       </c>
@@ -20263,7 +20563,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="138" spans="1:40">
+    <row r="138" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A138" s="31">
         <v>2018</v>
       </c>
@@ -20389,7 +20689,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="139" spans="1:40">
+    <row r="139" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A139" s="31">
         <v>2018</v>
       </c>
@@ -20515,7 +20815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:40">
+    <row r="140" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" s="31">
         <v>2018</v>
       </c>
@@ -20641,7 +20941,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="141" spans="1:40">
+    <row r="141" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" s="31">
         <v>2018</v>
       </c>
@@ -20767,7 +21067,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="142" spans="1:40">
+    <row r="142" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A142" s="31">
         <v>2018</v>
       </c>
@@ -20893,7 +21193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:40">
+    <row r="143" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A143" s="31">
         <v>2018</v>
       </c>
@@ -21019,7 +21319,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="144" spans="1:40">
+    <row r="144" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A144" s="31">
         <v>2018</v>
       </c>
@@ -21145,7 +21445,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="145" spans="1:40">
+    <row r="145" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A145" s="31">
         <v>2018</v>
       </c>
@@ -21271,7 +21571,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="146" spans="1:40">
+    <row r="146" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A146" s="31">
         <v>2018</v>
       </c>
@@ -21397,7 +21697,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="147" spans="1:40">
+    <row r="147" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A147" s="31">
         <v>2018</v>
       </c>
@@ -21523,7 +21823,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="148" spans="1:40">
+    <row r="148" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A148" s="31">
         <v>2018</v>
       </c>
@@ -21649,7 +21949,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="149" spans="1:40">
+    <row r="149" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A149" s="31">
         <v>2018</v>
       </c>
@@ -21775,7 +22075,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="150" spans="1:40">
+    <row r="150" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A150" s="31">
         <v>2018</v>
       </c>
@@ -21901,7 +22201,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="151" spans="1:40">
+    <row r="151" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A151" s="31">
         <v>2018</v>
       </c>
@@ -22027,7 +22327,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="152" spans="1:40">
+    <row r="152" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A152" s="31">
         <v>2018</v>
       </c>
@@ -22153,7 +22453,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="153" spans="1:40">
+    <row r="153" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A153" s="31">
         <v>2018</v>
       </c>
@@ -22279,7 +22579,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="154" spans="1:40">
+    <row r="154" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" s="31">
         <v>2018</v>
       </c>
@@ -22405,7 +22705,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="155" spans="1:40">
+    <row r="155" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A155" s="31">
         <v>2018</v>
       </c>
@@ -22531,7 +22831,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="156" spans="1:40">
+    <row r="156" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A156" s="31">
         <v>2018</v>
       </c>
@@ -22657,7 +22957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:40">
+    <row r="157" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" s="31">
         <v>2018</v>
       </c>
@@ -22783,7 +23083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:40">
+    <row r="158" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A158" s="31">
         <v>2018</v>
       </c>
@@ -22909,7 +23209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:40">
+    <row r="159" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" s="31">
         <v>2018</v>
       </c>
@@ -23035,7 +23335,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="160" spans="1:40">
+    <row r="160" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" s="31">
         <v>2018</v>
       </c>
@@ -23161,7 +23461,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="161" spans="1:40">
+    <row r="161" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A161" s="31">
         <v>2018</v>
       </c>
@@ -23287,7 +23587,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="162" spans="1:40">
+    <row r="162" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A162" s="31">
         <v>2018</v>
       </c>
@@ -23413,7 +23713,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="163" spans="1:40">
+    <row r="163" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A163" s="31">
         <v>2018</v>
       </c>
@@ -23539,7 +23839,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="164" spans="1:40">
+    <row r="164" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A164" s="31">
         <v>2018</v>
       </c>
@@ -23665,7 +23965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:40">
+    <row r="165" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A165" s="31">
         <v>2018</v>
       </c>
@@ -23791,7 +24091,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="166" spans="1:40">
+    <row r="166" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A166" s="31">
         <v>2018</v>
       </c>
@@ -23917,7 +24217,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="167" spans="1:40">
+    <row r="167" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A167" s="31">
         <v>2018</v>
       </c>
@@ -24043,7 +24343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:40">
+    <row r="168" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A168" s="31">
         <v>2018</v>
       </c>
@@ -24169,7 +24469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:40">
+    <row r="169" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A169" s="31">
         <v>2018</v>
       </c>
@@ -24295,7 +24595,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="170" spans="1:40">
+    <row r="170" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A170" s="31">
         <v>2018</v>
       </c>
@@ -24421,7 +24721,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="171" spans="1:40">
+    <row r="171" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A171" s="31">
         <v>2018</v>
       </c>
@@ -24547,7 +24847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:40">
+    <row r="172" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" s="31">
         <v>2018</v>
       </c>
@@ -24673,7 +24973,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="173" spans="1:40">
+    <row r="173" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A173" s="31">
         <v>2018</v>
       </c>
@@ -24799,7 +25099,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="174" spans="1:40">
+    <row r="174" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A174" s="31">
         <v>2018</v>
       </c>
@@ -24925,7 +25225,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="175" spans="1:40">
+    <row r="175" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A175" s="31">
         <v>2018</v>
       </c>
@@ -25051,7 +25351,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="176" spans="1:40">
+    <row r="176" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A176" s="31">
         <v>2018</v>
       </c>
@@ -25177,7 +25477,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="177" spans="1:40">
+    <row r="177" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A177" s="31">
         <v>2018</v>
       </c>
@@ -25303,7 +25603,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="178" spans="1:40">
+    <row r="178" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A178" s="31">
         <v>2018</v>
       </c>
@@ -25429,7 +25729,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="179" spans="1:40">
+    <row r="179" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A179" s="31">
         <v>2018</v>
       </c>
@@ -25555,7 +25855,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="180" spans="1:40">
+    <row r="180" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A180" s="31">
         <v>2018</v>
       </c>
@@ -25681,7 +25981,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="181" spans="1:40">
+    <row r="181" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A181" s="31">
         <v>2018</v>
       </c>
@@ -25807,7 +26107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:40">
+    <row r="182" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A182" s="31">
         <v>2018</v>
       </c>
@@ -25933,7 +26233,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="183" spans="1:40">
+    <row r="183" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A183" s="31">
         <v>2018</v>
       </c>
@@ -26059,7 +26359,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="184" spans="1:40">
+    <row r="184" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A184" s="31">
         <v>2018</v>
       </c>
@@ -26185,7 +26485,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="185" spans="1:40">
+    <row r="185" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A185" s="31">
         <v>2018</v>
       </c>
@@ -26311,7 +26611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:40">
+    <row r="186" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A186" s="31">
         <v>2018</v>
       </c>
@@ -26437,7 +26737,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="187" spans="1:40">
+    <row r="187" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A187" s="31">
         <v>2018</v>
       </c>
@@ -26563,7 +26863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:40">
+    <row r="188" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A188" s="31">
         <v>2018</v>
       </c>
@@ -26689,7 +26989,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="189" spans="1:40">
+    <row r="189" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A189" s="31">
         <v>2018</v>
       </c>
@@ -26815,7 +27115,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="190" spans="1:40">
+    <row r="190" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A190" s="31">
         <v>2018</v>
       </c>
@@ -26941,7 +27241,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="191" spans="1:40">
+    <row r="191" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A191" s="31">
         <v>2018</v>
       </c>
@@ -27067,7 +27367,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="192" spans="1:40">
+    <row r="192" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A192" s="31">
         <v>2018</v>
       </c>
@@ -27193,7 +27493,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="193" spans="1:40">
+    <row r="193" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A193" s="31">
         <v>2018</v>
       </c>
@@ -27319,7 +27619,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="194" spans="1:40">
+    <row r="194" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A194" s="31">
         <v>2018</v>
       </c>
@@ -27445,7 +27745,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="195" spans="1:40">
+    <row r="195" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A195" s="31">
         <v>2018</v>
       </c>
@@ -27571,7 +27871,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="196" spans="1:40">
+    <row r="196" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A196" s="31">
         <v>2018</v>
       </c>
@@ -27697,7 +27997,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="197" spans="1:40">
+    <row r="197" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A197" s="31">
         <v>2018</v>
       </c>
@@ -27823,7 +28123,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="198" spans="1:40">
+    <row r="198" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A198" s="31">
         <v>2018</v>
       </c>
@@ -27949,7 +28249,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="199" spans="1:40">
+    <row r="199" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A199" s="31">
         <v>2018</v>
       </c>
@@ -28075,7 +28375,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="200" spans="1:40">
+    <row r="200" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A200" s="31">
         <v>2018</v>
       </c>
@@ -28201,7 +28501,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="201" spans="1:40">
+    <row r="201" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A201" s="31">
         <v>2018</v>
       </c>
@@ -28327,7 +28627,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="202" spans="1:40">
+    <row r="202" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A202" s="31">
         <v>2018</v>
       </c>
@@ -28453,7 +28753,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="203" spans="1:40">
+    <row r="203" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A203" s="31">
         <v>2018</v>
       </c>
@@ -28579,7 +28879,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="204" spans="1:40">
+    <row r="204" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A204" s="31">
         <v>2018</v>
       </c>
@@ -28705,7 +29005,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="205" spans="1:40">
+    <row r="205" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A205" s="31">
         <v>2018</v>
       </c>
@@ -28831,7 +29131,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="206" spans="1:40">
+    <row r="206" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A206" s="31">
         <v>2018</v>
       </c>
@@ -28957,7 +29257,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="207" spans="1:40">
+    <row r="207" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A207" s="31">
         <v>2018</v>
       </c>
@@ -29083,7 +29383,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="208" spans="1:40">
+    <row r="208" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A208" s="31">
         <v>2018</v>
       </c>
@@ -29209,7 +29509,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="209" spans="1:40">
+    <row r="209" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A209" s="31">
         <v>2018</v>
       </c>
@@ -29335,7 +29635,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="210" spans="1:40">
+    <row r="210" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A210" s="31">
         <v>2018</v>
       </c>
@@ -29461,7 +29761,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="211" spans="1:40">
+    <row r="211" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A211" s="31">
         <v>2018</v>
       </c>
@@ -29587,7 +29887,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="212" spans="1:40">
+    <row r="212" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A212" s="31">
         <v>2018</v>
       </c>
@@ -29713,7 +30013,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="213" spans="1:40">
+    <row r="213" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A213" s="31">
         <v>2018</v>
       </c>
@@ -29839,7 +30139,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="214" spans="1:40">
+    <row r="214" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A214" s="31">
         <v>2018</v>
       </c>
@@ -29965,7 +30265,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="215" spans="1:40">
+    <row r="215" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A215" s="31">
         <v>2018</v>
       </c>
@@ -30091,7 +30391,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="216" spans="1:40">
+    <row r="216" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A216" s="31">
         <v>2018</v>
       </c>
@@ -30217,7 +30517,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="217" spans="1:40">
+    <row r="217" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A217" s="31">
         <v>2018</v>
       </c>
@@ -30343,7 +30643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:40">
+    <row r="218" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A218" s="31">
         <v>2018</v>
       </c>
@@ -30469,7 +30769,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="219" spans="1:40">
+    <row r="219" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A219" s="31">
         <v>2018</v>
       </c>
@@ -30595,7 +30895,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="220" spans="1:40">
+    <row r="220" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A220" s="31">
         <v>2018</v>
       </c>
@@ -30721,7 +31021,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="221" spans="1:40">
+    <row r="221" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A221" s="31">
         <v>2018</v>
       </c>
@@ -30847,7 +31147,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="222" spans="1:40">
+    <row r="222" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A222" s="31">
         <v>2018</v>
       </c>
@@ -30973,7 +31273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:40">
+    <row r="223" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A223" s="31">
         <v>2018</v>
       </c>
@@ -31099,7 +31399,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="224" spans="1:40">
+    <row r="224" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A224" s="31">
         <v>2018</v>
       </c>
@@ -31225,7 +31525,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="225" spans="1:40">
+    <row r="225" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A225" s="31">
         <v>2018</v>
       </c>
@@ -31351,7 +31651,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="226" spans="1:40">
+    <row r="226" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A226" s="31">
         <v>2018</v>
       </c>
@@ -31477,7 +31777,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="227" spans="1:40">
+    <row r="227" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A227" s="31">
         <v>2018</v>
       </c>
@@ -31603,7 +31903,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="228" spans="1:40">
+    <row r="228" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A228" s="31">
         <v>2018</v>
       </c>
@@ -31729,7 +32029,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="229" spans="1:40">
+    <row r="229" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A229" s="31">
         <v>2018</v>
       </c>
@@ -31855,7 +32155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:40">
+    <row r="230" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A230" s="31">
         <v>2018</v>
       </c>
@@ -31981,7 +32281,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="231" spans="1:40">
+    <row r="231" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A231" s="31">
         <v>2018</v>
       </c>
@@ -32107,7 +32407,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="232" spans="1:40">
+    <row r="232" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A232" s="31">
         <v>2018</v>
       </c>
@@ -32233,7 +32533,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="233" spans="1:40">
+    <row r="233" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A233" s="31">
         <v>2018</v>
       </c>
@@ -32359,7 +32659,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="234" spans="1:40">
+    <row r="234" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A234" s="31">
         <v>2018</v>
       </c>
@@ -32485,7 +32785,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="235" spans="1:40">
+    <row r="235" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A235" s="31">
         <v>2018</v>
       </c>
@@ -32611,7 +32911,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="236" spans="1:40">
+    <row r="236" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A236" s="31">
         <v>2018</v>
       </c>
@@ -32737,7 +33037,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="237" spans="1:40">
+    <row r="237" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A237" s="31">
         <v>2018</v>
       </c>
@@ -32863,7 +33163,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="238" spans="1:40">
+    <row r="238" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A238" s="31">
         <v>2018</v>
       </c>
@@ -32989,7 +33289,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="239" spans="1:40">
+    <row r="239" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A239" s="31">
         <v>2018</v>
       </c>
@@ -33115,7 +33415,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="240" spans="1:40">
+    <row r="240" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A240" s="31">
         <v>2018</v>
       </c>
@@ -33241,7 +33541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:40">
+    <row r="241" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A241" s="31">
         <v>2018</v>
       </c>
@@ -33367,7 +33667,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="242" spans="1:40">
+    <row r="242" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A242" s="31">
         <v>2018</v>
       </c>
@@ -33493,7 +33793,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="243" spans="1:40">
+    <row r="243" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A243" s="31">
         <v>2018</v>
       </c>
@@ -33619,7 +33919,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="244" spans="1:40">
+    <row r="244" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A244" s="31">
         <v>2018</v>
       </c>
@@ -33745,7 +34045,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="245" spans="1:40">
+    <row r="245" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A245" s="31">
         <v>2018</v>
       </c>
@@ -33871,7 +34171,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="246" spans="1:40">
+    <row r="246" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A246" s="31">
         <v>2018</v>
       </c>
@@ -33997,7 +34297,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="247" spans="1:40">
+    <row r="247" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A247" s="31">
         <v>2018</v>
       </c>
@@ -34123,7 +34423,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="248" spans="1:40">
+    <row r="248" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A248" s="31">
         <v>2018</v>
       </c>
@@ -34249,7 +34549,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="249" spans="1:40">
+    <row r="249" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A249" s="31">
         <v>2018</v>
       </c>
@@ -34375,7 +34675,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="250" spans="1:40">
+    <row r="250" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A250" s="31">
         <v>2018</v>
       </c>
@@ -34501,7 +34801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:40">
+    <row r="251" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A251" s="31">
         <v>2018</v>
       </c>
@@ -34627,7 +34927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:40">
+    <row r="252" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A252" s="31">
         <v>2018</v>
       </c>
@@ -34753,7 +35053,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="253" spans="1:40">
+    <row r="253" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A253" s="31">
         <v>2018</v>
       </c>
@@ -34879,7 +35179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:40">
+    <row r="254" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A254" s="31">
         <v>2018</v>
       </c>
@@ -35005,7 +35305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:40">
+    <row r="255" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A255" s="31">
         <v>2018</v>
       </c>
@@ -35131,7 +35431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:40">
+    <row r="256" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A256" s="31">
         <v>2018</v>
       </c>
@@ -35257,7 +35557,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="257" spans="1:40">
+    <row r="257" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A257" s="31">
         <v>2018</v>
       </c>
@@ -35383,7 +35683,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="258" spans="1:40">
+    <row r="258" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A258" s="31">
         <v>2018</v>
       </c>
@@ -35509,7 +35809,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="259" spans="1:40">
+    <row r="259" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A259" s="31">
         <v>2018</v>
       </c>
@@ -35635,7 +35935,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:40">
+    <row r="260" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A260" s="31">
         <v>2018</v>
       </c>
@@ -35761,7 +36061,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="261" spans="1:40">
+    <row r="261" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A261" s="31">
         <v>2018</v>
       </c>
@@ -35887,7 +36187,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="262" spans="1:40">
+    <row r="262" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A262" s="31">
         <v>2018</v>
       </c>
@@ -36013,7 +36313,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="263" spans="1:40">
+    <row r="263" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A263" s="31">
         <v>2018</v>
       </c>
@@ -36139,7 +36439,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="264" spans="1:40">
+    <row r="264" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A264" s="31">
         <v>2018</v>
       </c>
@@ -36265,7 +36565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:40">
+    <row r="265" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A265" s="31">
         <v>2018</v>
       </c>
@@ -36391,7 +36691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:40">
+    <row r="266" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A266" s="31">
         <v>2018</v>
       </c>
@@ -36517,7 +36817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:40">
+    <row r="267" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A267" s="31">
         <v>2018</v>
       </c>
@@ -36643,7 +36943,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="268" spans="1:40">
+    <row r="268" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A268" s="31">
         <v>2018</v>
       </c>
@@ -36769,7 +37069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:40">
+    <row r="269" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A269" s="31">
         <v>2018</v>
       </c>
@@ -36895,7 +37195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:40">
+    <row r="270" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A270" s="31">
         <v>2018</v>
       </c>
@@ -37021,7 +37321,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="271" spans="1:40">
+    <row r="271" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A271" s="31">
         <v>2018</v>
       </c>
@@ -37147,7 +37447,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="272" spans="1:40">
+    <row r="272" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A272" s="31">
         <v>2018</v>
       </c>
@@ -37273,7 +37573,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="273" spans="1:40">
+    <row r="273" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A273" s="31">
         <v>2018</v>
       </c>
@@ -37399,7 +37699,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="274" spans="1:40">
+    <row r="274" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A274" s="31">
         <v>2018</v>
       </c>
@@ -37525,7 +37825,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="275" spans="1:40">
+    <row r="275" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A275" s="31">
         <v>2018</v>
       </c>
@@ -37651,7 +37951,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="276" spans="1:40">
+    <row r="276" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A276" s="31">
         <v>2018</v>
       </c>
@@ -37777,7 +38077,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="277" spans="1:40">
+    <row r="277" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A277" s="31">
         <v>2018</v>
       </c>
@@ -37903,7 +38203,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="278" spans="1:40">
+    <row r="278" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A278" s="31">
         <v>2018</v>
       </c>
@@ -38029,7 +38329,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="279" spans="1:40">
+    <row r="279" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A279" s="31">
         <v>2018</v>
       </c>
@@ -38155,7 +38455,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="280" spans="1:40">
+    <row r="280" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A280" s="31">
         <v>2018</v>
       </c>
@@ -38281,7 +38581,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="281" spans="1:40">
+    <row r="281" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A281" s="31">
         <v>2018</v>
       </c>
@@ -38407,7 +38707,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="282" spans="1:40">
+    <row r="282" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A282" s="31">
         <v>2018</v>
       </c>
@@ -38533,7 +38833,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="283" spans="1:40">
+    <row r="283" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A283" s="31">
         <v>2018</v>
       </c>
@@ -38659,7 +38959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:40">
+    <row r="284" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A284" s="31">
         <v>2018</v>
       </c>
@@ -38785,7 +39085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:40">
+    <row r="285" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A285" s="31">
         <v>2018</v>
       </c>
@@ -38911,7 +39211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:40">
+    <row r="286" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A286" s="31">
         <v>2018</v>
       </c>
@@ -39037,7 +39337,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="287" spans="1:40">
+    <row r="287" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A287" s="31">
         <v>2018</v>
       </c>
@@ -39163,7 +39463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:40">
+    <row r="288" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A288" s="31">
         <v>2018</v>
       </c>
@@ -39289,7 +39589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:40">
+    <row r="289" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A289" s="31">
         <v>2018</v>
       </c>
@@ -39415,7 +39715,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="290" spans="1:40">
+    <row r="290" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A290" s="31">
         <v>2018</v>
       </c>
@@ -39541,7 +39841,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="291" spans="1:40">
+    <row r="291" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A291" s="31">
         <v>2018</v>
       </c>
@@ -39667,7 +39967,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="292" spans="1:40">
+    <row r="292" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A292" s="31">
         <v>2018</v>
       </c>
@@ -39793,7 +40093,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="293" spans="1:40">
+    <row r="293" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A293" s="31">
         <v>2018</v>
       </c>
@@ -39919,7 +40219,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="294" spans="1:40">
+    <row r="294" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A294" s="31">
         <v>2018</v>
       </c>
@@ -40045,7 +40345,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="295" spans="1:40">
+    <row r="295" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A295" s="31">
         <v>2018</v>
       </c>
@@ -40171,7 +40471,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="296" spans="1:40">
+    <row r="296" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A296" s="31">
         <v>2018</v>
       </c>
@@ -40297,7 +40597,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="297" spans="1:40">
+    <row r="297" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A297" s="31">
         <v>2018</v>
       </c>
@@ -40423,7 +40723,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="298" spans="1:40">
+    <row r="298" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A298" s="31">
         <v>2018</v>
       </c>
@@ -40549,7 +40849,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="299" spans="1:40">
+    <row r="299" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A299" s="31">
         <v>2018</v>
       </c>
@@ -40675,7 +40975,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="300" spans="1:40">
+    <row r="300" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A300" s="31">
         <v>2018</v>
       </c>
@@ -40801,7 +41101,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="301" spans="1:40">
+    <row r="301" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A301" s="31">
         <v>2018</v>
       </c>
@@ -40927,7 +41227,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="302" spans="1:40">
+    <row r="302" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A302" s="31">
         <v>2018</v>
       </c>
@@ -41053,7 +41353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:40">
+    <row r="303" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A303" s="31">
         <v>2018</v>
       </c>
@@ -41179,7 +41479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:40">
+    <row r="304" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A304" s="31">
         <v>2018</v>
       </c>
@@ -41305,7 +41605,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="305" spans="1:40">
+    <row r="305" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A305" s="31">
         <v>2018</v>
       </c>
@@ -41431,7 +41731,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="306" spans="1:40">
+    <row r="306" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A306" s="31">
         <v>2018</v>
       </c>
@@ -41557,7 +41857,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="307" spans="1:40">
+    <row r="307" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A307" s="31">
         <v>2018</v>
       </c>
@@ -41683,7 +41983,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="308" spans="1:40">
+    <row r="308" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A308" s="31">
         <v>2018</v>
       </c>
@@ -41809,7 +42109,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="309" spans="1:40">
+    <row r="309" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A309" s="31">
         <v>2018</v>
       </c>
@@ -41935,7 +42235,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="310" spans="1:40">
+    <row r="310" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A310" s="31">
         <v>2018</v>
       </c>
@@ -42061,7 +42361,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="311" spans="1:40">
+    <row r="311" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A311" s="31">
         <v>2018</v>
       </c>
@@ -42187,7 +42487,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="312" spans="1:40">
+    <row r="312" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A312" s="31">
         <v>2018</v>
       </c>
@@ -42313,7 +42613,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="313" spans="1:40">
+    <row r="313" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A313" s="31">
         <v>2018</v>
       </c>
@@ -42439,7 +42739,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="314" spans="1:40">
+    <row r="314" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A314" s="31">
         <v>2018</v>
       </c>
@@ -42565,7 +42865,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="315" spans="1:40">
+    <row r="315" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A315" s="31">
         <v>2018</v>
       </c>
@@ -42691,7 +42991,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="316" spans="1:40">
+    <row r="316" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A316" s="31">
         <v>2018</v>
       </c>
@@ -42817,7 +43117,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="317" spans="1:40">
+    <row r="317" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A317" s="31">
         <v>2018</v>
       </c>
@@ -42943,7 +43243,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="318" spans="1:40">
+    <row r="318" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A318" s="31">
         <v>2018</v>
       </c>
@@ -43069,7 +43369,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="319" spans="1:40">
+    <row r="319" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A319" s="31">
         <v>2018</v>
       </c>
@@ -43195,7 +43495,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="320" spans="1:40">
+    <row r="320" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A320" s="31">
         <v>2018</v>
       </c>
@@ -43321,7 +43621,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="321" spans="1:40">
+    <row r="321" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A321" s="31">
         <v>2018</v>
       </c>
@@ -43447,7 +43747,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="322" spans="1:40">
+    <row r="322" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A322" s="31">
         <v>2018</v>
       </c>
@@ -43573,7 +43873,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="323" spans="1:40">
+    <row r="323" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A323" s="31">
         <v>2018</v>
       </c>
@@ -43699,7 +43999,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="324" spans="1:40">
+    <row r="324" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A324" s="31">
         <v>2018</v>
       </c>
@@ -43825,7 +44125,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="325" spans="1:40">
+    <row r="325" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A325" s="31">
         <v>2018</v>
       </c>
@@ -43951,7 +44251,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="326" spans="1:40">
+    <row r="326" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A326" s="31">
         <v>2018</v>
       </c>
@@ -44077,7 +44377,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="327" spans="1:40">
+    <row r="327" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A327" s="31">
         <v>2018</v>
       </c>
@@ -44203,7 +44503,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="328" spans="1:40">
+    <row r="328" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A328" s="31">
         <v>2018</v>
       </c>
@@ -44329,7 +44629,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="329" spans="1:40">
+    <row r="329" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A329" s="31">
         <v>2018</v>
       </c>
@@ -44455,7 +44755,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="330" spans="1:40">
+    <row r="330" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A330" s="31">
         <v>2018</v>
       </c>
@@ -44581,7 +44881,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="331" spans="1:40">
+    <row r="331" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A331" s="31">
         <v>2018</v>
       </c>
@@ -44707,7 +45007,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="332" spans="1:40">
+    <row r="332" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A332" s="31">
         <v>2018</v>
       </c>
@@ -44833,7 +45133,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="333" spans="1:40">
+    <row r="333" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A333" s="31">
         <v>2018</v>
       </c>
@@ -44959,7 +45259,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="334" spans="1:40">
+    <row r="334" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A334" s="31">
         <v>2018</v>
       </c>
@@ -45085,7 +45385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:40">
+    <row r="335" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A335" s="31">
         <v>2018</v>
       </c>
@@ -45211,7 +45511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:40">
+    <row r="336" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A336" s="31">
         <v>2018</v>
       </c>
@@ -45337,7 +45637,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="337" spans="1:40">
+    <row r="337" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A337" s="31">
         <v>2018</v>
       </c>
@@ -45463,7 +45763,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="338" spans="1:40">
+    <row r="338" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A338" s="31">
         <v>2018</v>
       </c>
@@ -45589,7 +45889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:40">
+    <row r="339" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A339" s="31">
         <v>2018</v>
       </c>
@@ -45715,7 +46015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:40">
+    <row r="340" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A340" s="31">
         <v>2018</v>
       </c>
@@ -45841,7 +46141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:40">
+    <row r="341" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A341" s="31">
         <v>2018</v>
       </c>
@@ -45967,7 +46267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:40">
+    <row r="342" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A342" s="31">
         <v>2018</v>
       </c>
@@ -46093,7 +46393,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="343" spans="1:40">
+    <row r="343" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A343" s="31">
         <v>2018</v>
       </c>
@@ -46219,7 +46519,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="344" spans="1:40">
+    <row r="344" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A344" s="31">
         <v>2018</v>
       </c>
@@ -46345,7 +46645,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="345" spans="1:40">
+    <row r="345" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A345" s="31">
         <v>2018</v>
       </c>
@@ -46471,7 +46771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:40">
+    <row r="346" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A346" s="31">
         <v>2018</v>
       </c>
@@ -46597,7 +46897,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="347" spans="1:40">
+    <row r="347" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A347" s="31">
         <v>2018</v>
       </c>
@@ -46723,7 +47023,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="348" spans="1:40">
+    <row r="348" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A348" s="31">
         <v>2018</v>
       </c>
@@ -46849,7 +47149,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="349" spans="1:40">
+    <row r="349" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A349" s="31">
         <v>2018</v>
       </c>
@@ -46975,7 +47275,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="350" spans="1:40">
+    <row r="350" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A350" s="31">
         <v>2018</v>
       </c>
@@ -47101,7 +47401,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="351" spans="1:40">
+    <row r="351" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A351" s="31">
         <v>2018</v>
       </c>
@@ -47227,7 +47527,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="352" spans="1:40">
+    <row r="352" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A352" s="31">
         <v>2018</v>
       </c>
@@ -47353,7 +47653,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="353" spans="1:40">
+    <row r="353" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A353" s="31">
         <v>2018</v>
       </c>
@@ -47479,7 +47779,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="354" spans="1:40">
+    <row r="354" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A354" s="31">
         <v>2018</v>
       </c>
@@ -47605,7 +47905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:40">
+    <row r="355" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A355" s="31">
         <v>2018</v>
       </c>
@@ -47731,7 +48031,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="356" spans="1:40">
+    <row r="356" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A356" s="31">
         <v>2018</v>
       </c>
@@ -47857,7 +48157,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="357" spans="1:40">
+    <row r="357" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A357" s="31">
         <v>2018</v>
       </c>
@@ -47983,7 +48283,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="358" spans="1:40">
+    <row r="358" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A358" s="31">
         <v>2018</v>
       </c>
@@ -48109,7 +48409,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="359" spans="1:40">
+    <row r="359" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A359" s="31">
         <v>2018</v>
       </c>
@@ -48235,7 +48535,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="360" spans="1:40">
+    <row r="360" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A360" s="31">
         <v>2018</v>
       </c>
@@ -48361,7 +48661,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="361" spans="1:40">
+    <row r="361" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A361" s="31">
         <v>2018</v>
       </c>
@@ -48487,7 +48787,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="362" spans="1:40">
+    <row r="362" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A362" s="31">
         <v>2018</v>
       </c>
@@ -48613,7 +48913,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="363" spans="1:40">
+    <row r="363" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A363" s="31">
         <v>2018</v>
       </c>
@@ -48739,7 +49039,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="364" spans="1:40">
+    <row r="364" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A364" s="31">
         <v>2018</v>
       </c>
@@ -48865,7 +49165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:40">
+    <row r="365" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A365" s="31">
         <v>2018</v>
       </c>
@@ -48991,7 +49291,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="366" spans="1:40">
+    <row r="366" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A366" s="31">
         <v>2018</v>
       </c>
@@ -49117,7 +49417,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="367" spans="1:40">
+    <row r="367" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A367" s="31">
         <v>2018</v>
       </c>
@@ -49243,7 +49543,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="368" spans="1:40">
+    <row r="368" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A368" s="31">
         <v>2018</v>
       </c>
@@ -49369,7 +49669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:40">
+    <row r="369" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A369" s="31">
         <v>2018</v>
       </c>
@@ -49495,7 +49795,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="370" spans="1:40">
+    <row r="370" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A370" s="31">
         <v>2018</v>
       </c>
@@ -49621,7 +49921,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="371" spans="1:40">
+    <row r="371" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A371" s="31">
         <v>2018</v>
       </c>
@@ -49747,7 +50047,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="372" spans="1:40">
+    <row r="372" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A372" s="31">
         <v>2018</v>
       </c>
@@ -49873,7 +50173,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="373" spans="1:40">
+    <row r="373" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A373" s="31">
         <v>2018</v>
       </c>
@@ -49999,7 +50299,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="374" spans="1:40">
+    <row r="374" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A374" s="31">
         <v>2018</v>
       </c>
@@ -50125,7 +50425,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="375" spans="1:40">
+    <row r="375" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A375" s="31">
         <v>2018</v>
       </c>
@@ -50251,7 +50551,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="376" spans="1:40">
+    <row r="376" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A376" s="31">
         <v>2018</v>
       </c>
@@ -50377,7 +50677,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="377" spans="1:40">
+    <row r="377" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A377" s="31">
         <v>2018</v>
       </c>
@@ -50503,7 +50803,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="378" spans="1:40">
+    <row r="378" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A378" s="31">
         <v>2018</v>
       </c>
@@ -50629,7 +50929,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="379" spans="1:40">
+    <row r="379" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A379" s="31">
         <v>2018</v>
       </c>
@@ -50755,7 +51055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:40">
+    <row r="380" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A380" s="31">
         <v>2018</v>
       </c>
@@ -50881,7 +51181,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="381" spans="1:40">
+    <row r="381" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A381" s="31">
         <v>2018</v>
       </c>
@@ -51007,7 +51307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:40">
+    <row r="382" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A382" s="31">
         <v>2018</v>
       </c>
@@ -51133,7 +51433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:40">
+    <row r="383" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A383" s="31">
         <v>2018</v>
       </c>
@@ -51259,7 +51559,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="384" spans="1:40">
+    <row r="384" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A384" s="31">
         <v>2018</v>
       </c>
@@ -51385,7 +51685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:40">
+    <row r="385" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A385" s="31">
         <v>2018</v>
       </c>
@@ -51511,7 +51811,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="386" spans="1:40">
+    <row r="386" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A386" s="31">
         <v>2018</v>
       </c>
@@ -51637,7 +51937,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="387" spans="1:40">
+    <row r="387" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A387" s="31">
         <v>2018</v>
       </c>
@@ -51763,7 +52063,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="388" spans="1:40">
+    <row r="388" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A388" s="31">
         <v>2018</v>
       </c>
@@ -51889,7 +52189,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="389" spans="1:40">
+    <row r="389" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A389" s="31">
         <v>2018</v>
       </c>
@@ -52015,7 +52315,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="390" spans="1:40">
+    <row r="390" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A390" s="31">
         <v>2018</v>
       </c>
@@ -52141,7 +52441,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="391" spans="1:40">
+    <row r="391" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A391" s="31">
         <v>2018</v>
       </c>
@@ -52267,7 +52567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:40">
+    <row r="392" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A392" s="31">
         <v>2018</v>
       </c>
@@ -52393,7 +52693,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="393" spans="1:40">
+    <row r="393" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A393" s="31">
         <v>2018</v>
       </c>
@@ -52519,7 +52819,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="394" spans="1:40">
+    <row r="394" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A394" s="31">
         <v>2018</v>
       </c>
@@ -52645,7 +52945,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="395" spans="1:40">
+    <row r="395" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A395" s="31">
         <v>2018</v>
       </c>
@@ -52771,7 +53071,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="396" spans="1:40">
+    <row r="396" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A396" s="31">
         <v>2018</v>
       </c>
@@ -52897,7 +53197,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="397" spans="1:40">
+    <row r="397" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A397" s="31">
         <v>2018</v>
       </c>
@@ -53023,7 +53323,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="398" spans="1:40">
+    <row r="398" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A398" s="31">
         <v>2018</v>
       </c>
@@ -53149,7 +53449,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="399" spans="1:40">
+    <row r="399" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A399" s="31">
         <v>2018</v>
       </c>
@@ -53275,7 +53575,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="400" spans="1:40">
+    <row r="400" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A400" s="31">
         <v>2018</v>
       </c>
@@ -53401,7 +53701,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="401" spans="1:40">
+    <row r="401" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A401" s="31">
         <v>2018</v>
       </c>
@@ -53527,7 +53827,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="402" spans="1:40">
+    <row r="402" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A402" s="31">
         <v>2018</v>
       </c>
@@ -53653,7 +53953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:40">
+    <row r="403" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A403" s="31">
         <v>2018</v>
       </c>
@@ -53779,7 +54079,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="404" spans="1:40">
+    <row r="404" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A404" s="31">
         <v>2018</v>
       </c>
@@ -53905,7 +54205,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="405" spans="1:40">
+    <row r="405" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A405" s="31">
         <v>2018</v>
       </c>
@@ -54031,7 +54331,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="406" spans="1:40">
+    <row r="406" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A406" s="31">
         <v>2018</v>
       </c>
@@ -54157,7 +54457,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="407" spans="1:40">
+    <row r="407" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A407" s="31">
         <v>2018</v>
       </c>
@@ -54283,7 +54583,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="408" spans="1:40">
+    <row r="408" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A408" s="31">
         <v>2018</v>
       </c>
@@ -54409,7 +54709,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="409" spans="1:40">
+    <row r="409" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A409" s="31">
         <v>2018</v>
       </c>
@@ -54535,7 +54835,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="410" spans="1:40">
+    <row r="410" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A410" s="31">
         <v>2018</v>
       </c>
@@ -54661,7 +54961,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="411" spans="1:40">
+    <row r="411" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A411" s="31">
         <v>2018</v>
       </c>
@@ -54787,7 +55087,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="412" spans="1:40">
+    <row r="412" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A412" s="31">
         <v>2018</v>
       </c>
@@ -54913,7 +55213,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="413" spans="1:40">
+    <row r="413" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A413" s="31">
         <v>2018</v>
       </c>
@@ -55039,7 +55339,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="414" spans="1:40">
+    <row r="414" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A414" s="31">
         <v>2018</v>
       </c>
@@ -55165,7 +55465,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="415" spans="1:40">
+    <row r="415" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A415" s="31">
         <v>2018</v>
       </c>
@@ -55291,7 +55591,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="416" spans="1:40">
+    <row r="416" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A416" s="31">
         <v>2018</v>
       </c>
@@ -55417,7 +55717,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="417" spans="1:40">
+    <row r="417" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A417" s="31">
         <v>2018</v>
       </c>
@@ -55543,7 +55843,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="418" spans="1:40">
+    <row r="418" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A418" s="31">
         <v>2018</v>
       </c>
@@ -55669,7 +55969,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="419" spans="1:40">
+    <row r="419" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A419" s="31">
         <v>2018</v>
       </c>
@@ -55795,7 +56095,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="420" spans="1:40">
+    <row r="420" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A420" s="31">
         <v>2018</v>
       </c>
@@ -55921,7 +56221,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="421" spans="1:40">
+    <row r="421" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A421" s="31">
         <v>2018</v>
       </c>
@@ -56047,7 +56347,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="422" spans="1:40">
+    <row r="422" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A422" s="31">
         <v>2018</v>
       </c>
@@ -56173,7 +56473,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="423" spans="1:40">
+    <row r="423" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A423" s="31">
         <v>2018</v>
       </c>
@@ -56299,7 +56599,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="424" spans="1:40">
+    <row r="424" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A424" s="31">
         <v>2018</v>
       </c>
@@ -56425,7 +56725,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="425" spans="1:40">
+    <row r="425" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A425" s="31">
         <v>2018</v>
       </c>
@@ -56551,7 +56851,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="426" spans="1:40">
+    <row r="426" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A426" s="31">
         <v>2018</v>
       </c>
@@ -56677,7 +56977,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="427" spans="1:40">
+    <row r="427" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A427" s="31">
         <v>2018</v>
       </c>
@@ -56803,7 +57103,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="428" spans="1:40">
+    <row r="428" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A428" s="31">
         <v>2018</v>
       </c>
@@ -56929,7 +57229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:40">
+    <row r="429" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A429" s="31">
         <v>2018</v>
       </c>
@@ -57055,7 +57355,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="430" spans="1:40">
+    <row r="430" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A430" s="31">
         <v>2018</v>
       </c>
@@ -57181,7 +57481,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="431" spans="1:40">
+    <row r="431" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A431" s="31">
         <v>2018</v>
       </c>
@@ -57307,7 +57607,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="432" spans="1:40">
+    <row r="432" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A432" s="31">
         <v>2018</v>
       </c>
@@ -57454,43 +57754,3705 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEB4A9D1-3E9E-354F-825E-77289F5EEC55}">
+  <dimension ref="A1:E127"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="30.83203125" style="40" customWidth="1"/>
+    <col min="2" max="16384" width="10.83203125" style="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="41" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="41" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="41" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="41" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="40" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B9" s="40" t="s">
+        <v>580</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>579</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>578</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="41" t="s">
+        <v>576</v>
+      </c>
+      <c r="B11" s="40">
+        <v>1075.643</v>
+      </c>
+      <c r="C11" s="40">
+        <v>940.94600000000003</v>
+      </c>
+      <c r="D11" s="40">
+        <v>990.35699999999997</v>
+      </c>
+      <c r="E11" s="40">
+        <v>972.57500000000005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="40" t="s">
+        <v>567</v>
+      </c>
+      <c r="B13" s="40">
+        <v>14.978999999999999</v>
+      </c>
+      <c r="C13" s="40">
+        <v>40.679000000000002</v>
+      </c>
+      <c r="D13" s="40">
+        <v>58.780999999999999</v>
+      </c>
+      <c r="E13" s="40">
+        <v>65.11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="40" t="s">
+        <v>570</v>
+      </c>
+      <c r="B14" s="40">
+        <v>330.28100000000001</v>
+      </c>
+      <c r="C14" s="40">
+        <v>245.6</v>
+      </c>
+      <c r="D14" s="40">
+        <v>244.46799999999999</v>
+      </c>
+      <c r="E14" s="40">
+        <v>243.30699999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="40" t="s">
+        <v>575</v>
+      </c>
+      <c r="B15" s="40">
+        <v>365.73700000000002</v>
+      </c>
+      <c r="C15" s="40">
+        <v>300.27600000000001</v>
+      </c>
+      <c r="D15" s="40">
+        <v>310.20100000000002</v>
+      </c>
+      <c r="E15" s="40">
+        <v>283.077</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="B16" s="40">
+        <v>365.73700000000002</v>
+      </c>
+      <c r="C16" s="40">
+        <v>300.27600000000001</v>
+      </c>
+      <c r="D16" s="40">
+        <v>310.20100000000002</v>
+      </c>
+      <c r="E16" s="40">
+        <v>283.077</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="40" t="s">
+        <v>573</v>
+      </c>
+      <c r="B17" s="40">
+        <v>0</v>
+      </c>
+      <c r="C17" s="40">
+        <v>0</v>
+      </c>
+      <c r="D17" s="40">
+        <v>0</v>
+      </c>
+      <c r="E17" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="B18" s="40">
+        <v>0</v>
+      </c>
+      <c r="C18" s="40">
+        <v>0</v>
+      </c>
+      <c r="D18" s="40">
+        <v>0</v>
+      </c>
+      <c r="E18" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="40" t="s">
+        <v>563</v>
+      </c>
+      <c r="B19" s="40">
+        <v>35.445999999999998</v>
+      </c>
+      <c r="C19" s="40">
+        <v>39.488999999999997</v>
+      </c>
+      <c r="D19" s="40">
+        <v>37.197000000000003</v>
+      </c>
+      <c r="E19" s="40">
+        <v>39.177999999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="40" t="s">
+        <v>561</v>
+      </c>
+      <c r="B20" s="40">
+        <f t="shared" ref="B20:E20" si="0">B29+B37+B40+B59</f>
+        <v>407.32600000000002</v>
+      </c>
+      <c r="C20" s="40">
+        <f t="shared" si="0"/>
+        <v>401.18600000000004</v>
+      </c>
+      <c r="D20" s="40">
+        <f t="shared" si="0"/>
+        <v>450.37800000000004</v>
+      </c>
+      <c r="E20" s="40">
+        <f t="shared" si="0"/>
+        <v>422.85899999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="41" t="s">
+        <v>571</v>
+      </c>
+      <c r="B22" s="40">
+        <v>914.87900000000002</v>
+      </c>
+      <c r="C22" s="40">
+        <v>796.59</v>
+      </c>
+      <c r="D22" s="40">
+        <v>833.62199999999996</v>
+      </c>
+      <c r="E22" s="40">
+        <v>822.15300000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="40" t="s">
+        <v>567</v>
+      </c>
+      <c r="B23" s="40">
+        <v>9.0139999999999993</v>
+      </c>
+      <c r="C23" s="40">
+        <v>34.17</v>
+      </c>
+      <c r="D23" s="40">
+        <v>52.06</v>
+      </c>
+      <c r="E23" s="40">
+        <v>56.64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="40" t="s">
+        <v>570</v>
+      </c>
+      <c r="B24" s="40">
+        <v>330.28100000000001</v>
+      </c>
+      <c r="C24" s="40">
+        <v>245.6</v>
+      </c>
+      <c r="D24" s="40">
+        <v>244.46799999999999</v>
+      </c>
+      <c r="E24" s="40">
+        <v>243.30699999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="41" t="s">
+        <v>566</v>
+      </c>
+      <c r="B25" s="40">
+        <v>289.541</v>
+      </c>
+      <c r="C25" s="40">
+        <v>239.102</v>
+      </c>
+      <c r="D25" s="40">
+        <v>246.976</v>
+      </c>
+      <c r="E25" s="40">
+        <v>224.56800000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="40" t="s">
+        <v>565</v>
+      </c>
+      <c r="B26" s="40">
+        <v>289.541</v>
+      </c>
+      <c r="C26" s="40">
+        <v>239.102</v>
+      </c>
+      <c r="D26" s="40">
+        <v>246.976</v>
+      </c>
+      <c r="E26" s="40">
+        <v>224.56800000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="40" t="s">
+        <v>569</v>
+      </c>
+      <c r="B27" s="40">
+        <v>0</v>
+      </c>
+      <c r="C27" s="40">
+        <v>0</v>
+      </c>
+      <c r="D27" s="40">
+        <v>0</v>
+      </c>
+      <c r="E27" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="40" t="s">
+        <v>563</v>
+      </c>
+      <c r="B28" s="40">
+        <v>25.946000000000002</v>
+      </c>
+      <c r="C28" s="40">
+        <v>27.661999999999999</v>
+      </c>
+      <c r="D28" s="40">
+        <v>25.202999999999999</v>
+      </c>
+      <c r="E28" s="40">
+        <v>26.003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="40" t="s">
+        <v>561</v>
+      </c>
+      <c r="B29" s="40">
+        <v>260.09699999999998</v>
+      </c>
+      <c r="C29" s="40">
+        <v>250.06</v>
+      </c>
+      <c r="D29" s="40">
+        <v>264.91500000000002</v>
+      </c>
+      <c r="E29" s="40">
+        <v>271.63400000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="41" t="s">
+        <v>568</v>
+      </c>
+      <c r="B31" s="40">
+        <v>145.40700000000001</v>
+      </c>
+      <c r="C31" s="40">
+        <v>130.30699999999999</v>
+      </c>
+      <c r="D31" s="40">
+        <v>141.244</v>
+      </c>
+      <c r="E31" s="40">
+        <v>136.94800000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="40" t="s">
+        <v>567</v>
+      </c>
+      <c r="B32" s="40">
+        <v>5.9649999999999999</v>
+      </c>
+      <c r="C32" s="40">
+        <v>6.5090000000000003</v>
+      </c>
+      <c r="D32" s="40">
+        <v>6.7210000000000001</v>
+      </c>
+      <c r="E32" s="40">
+        <v>8.4700000000000006</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="41" t="s">
+        <v>566</v>
+      </c>
+      <c r="B33" s="40">
+        <v>76.195999999999998</v>
+      </c>
+      <c r="C33" s="40">
+        <v>61.173999999999999</v>
+      </c>
+      <c r="D33" s="40">
+        <v>63.225000000000001</v>
+      </c>
+      <c r="E33" s="40">
+        <v>58.509</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="40" t="s">
+        <v>565</v>
+      </c>
+      <c r="B34" s="40">
+        <v>76.195999999999998</v>
+      </c>
+      <c r="C34" s="40">
+        <v>61.173999999999999</v>
+      </c>
+      <c r="D34" s="40">
+        <v>63.225000000000001</v>
+      </c>
+      <c r="E34" s="40">
+        <v>58.509</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="40" t="s">
+        <v>564</v>
+      </c>
+      <c r="B35" s="40">
+        <v>0</v>
+      </c>
+      <c r="C35" s="40">
+        <v>0</v>
+      </c>
+      <c r="D35" s="40">
+        <v>0</v>
+      </c>
+      <c r="E35" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="40" t="s">
+        <v>563</v>
+      </c>
+      <c r="B36" s="40">
+        <v>9.5</v>
+      </c>
+      <c r="C36" s="40">
+        <v>11.827</v>
+      </c>
+      <c r="D36" s="40">
+        <v>11.994</v>
+      </c>
+      <c r="E36" s="40">
+        <v>13.175000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="40" t="s">
+        <v>561</v>
+      </c>
+      <c r="B37" s="40">
+        <v>53.747</v>
+      </c>
+      <c r="C37" s="40">
+        <v>50.8</v>
+      </c>
+      <c r="D37" s="40">
+        <v>59.305</v>
+      </c>
+      <c r="E37" s="40">
+        <v>56.793999999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="41" t="s">
+        <v>562</v>
+      </c>
+      <c r="B39" s="40">
+        <v>15.356</v>
+      </c>
+      <c r="C39" s="40">
+        <v>14.048999999999999</v>
+      </c>
+      <c r="D39" s="40">
+        <v>15.49</v>
+      </c>
+      <c r="E39" s="40">
+        <v>13.474</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="40" t="s">
+        <v>561</v>
+      </c>
+      <c r="B40" s="40">
+        <v>15.356</v>
+      </c>
+      <c r="C40" s="40">
+        <v>13.92</v>
+      </c>
+      <c r="D40" s="40">
+        <v>15.343</v>
+      </c>
+      <c r="E40" s="40">
+        <v>13.313000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="41" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="40" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="40" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="41" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="41" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="41" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="41" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="40" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B55" s="40" t="s">
+        <v>580</v>
+      </c>
+      <c r="C55" s="40" t="s">
+        <v>579</v>
+      </c>
+      <c r="D55" s="40" t="s">
+        <v>578</v>
+      </c>
+      <c r="E55" s="40" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="40" t="s">
+        <v>615</v>
+      </c>
+      <c r="B57" s="40">
+        <v>1418.0450000000001</v>
+      </c>
+      <c r="C57" s="40">
+        <v>1152.6669999999999</v>
+      </c>
+      <c r="D57" s="40">
+        <v>1476.99</v>
+      </c>
+      <c r="E57" s="40">
+        <v>1238.9580000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="40" t="s">
+        <v>610</v>
+      </c>
+      <c r="B58" s="40">
+        <v>630.56700000000001</v>
+      </c>
+      <c r="C58" s="40">
+        <v>380.14299999999997</v>
+      </c>
+      <c r="D58" s="40">
+        <v>646.36300000000006</v>
+      </c>
+      <c r="E58" s="40">
+        <v>405.18700000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="40" t="s">
+        <v>617</v>
+      </c>
+      <c r="B59" s="40">
+        <f t="shared" ref="B59:E59" si="1">B65+B68+B71+B77+B86+B89+B116</f>
+        <v>78.126000000000005</v>
+      </c>
+      <c r="C59" s="40">
+        <f t="shared" si="1"/>
+        <v>86.405999999999992</v>
+      </c>
+      <c r="D59" s="40">
+        <f t="shared" si="1"/>
+        <v>110.81499999999998</v>
+      </c>
+      <c r="E59" s="40">
+        <f t="shared" si="1"/>
+        <v>81.117999999999995</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="40" t="s">
+        <v>614</v>
+      </c>
+      <c r="B61" s="40">
+        <v>79.837000000000003</v>
+      </c>
+      <c r="C61" s="40">
+        <v>67.655000000000001</v>
+      </c>
+      <c r="D61" s="40">
+        <v>68.144999999999996</v>
+      </c>
+      <c r="E61" s="40">
+        <v>66.227999999999994</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="40" t="s">
+        <v>610</v>
+      </c>
+      <c r="B62" s="40">
+        <v>47.292999999999999</v>
+      </c>
+      <c r="C62" s="40">
+        <v>41.795000000000002</v>
+      </c>
+      <c r="D62" s="40">
+        <v>42.357999999999997</v>
+      </c>
+      <c r="E62" s="40">
+        <v>41.295000000000002</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="40" t="s">
+        <v>613</v>
+      </c>
+      <c r="B64" s="40">
+        <v>16.256</v>
+      </c>
+      <c r="C64" s="40">
+        <v>8.4410000000000007</v>
+      </c>
+      <c r="D64" s="40">
+        <v>8.4350000000000005</v>
+      </c>
+      <c r="E64" s="40">
+        <v>8.7430000000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B65" s="40">
+        <v>2.101</v>
+      </c>
+      <c r="C65" s="40">
+        <v>2.8180000000000001</v>
+      </c>
+      <c r="D65" s="40">
+        <v>2.8250000000000002</v>
+      </c>
+      <c r="E65" s="40">
+        <v>2.9740000000000002</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" s="40" t="s">
+        <v>612</v>
+      </c>
+      <c r="B67" s="40">
+        <v>36.31</v>
+      </c>
+      <c r="C67" s="40">
+        <v>69.132999999999996</v>
+      </c>
+      <c r="D67" s="40">
+        <v>83.954999999999998</v>
+      </c>
+      <c r="E67" s="40">
+        <v>69.22</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B68" s="40">
+        <v>4.09</v>
+      </c>
+      <c r="C68" s="40">
+        <v>8.968</v>
+      </c>
+      <c r="D68" s="40">
+        <v>8.75</v>
+      </c>
+      <c r="E68" s="40">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" s="40" t="s">
+        <v>611</v>
+      </c>
+      <c r="B70" s="40">
+        <v>0.55200000000000005</v>
+      </c>
+      <c r="C70" s="40">
+        <v>12.728</v>
+      </c>
+      <c r="D70" s="40">
+        <v>10.007999999999999</v>
+      </c>
+      <c r="E70" s="40">
+        <v>11.958</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" s="40" t="s">
+        <v>610</v>
+      </c>
+      <c r="B71" s="40">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="C71" s="40">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D71" s="40">
+        <v>1.01</v>
+      </c>
+      <c r="E71" s="40">
+        <v>3.5089999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" s="40" t="s">
+        <v>609</v>
+      </c>
+      <c r="B73" s="40" t="s">
+        <v>589</v>
+      </c>
+      <c r="C73" s="40">
+        <v>12.438000000000001</v>
+      </c>
+      <c r="D73" s="40">
+        <v>9.3460000000000001</v>
+      </c>
+      <c r="E73" s="40">
+        <v>11.957000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B74" s="40" t="s">
+        <v>589</v>
+      </c>
+      <c r="C74" s="40">
+        <v>3.5750000000000002</v>
+      </c>
+      <c r="D74" s="40">
+        <v>0.45</v>
+      </c>
+      <c r="E74" s="40">
+        <v>3.452</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" s="40" t="s">
+        <v>608</v>
+      </c>
+      <c r="B76" s="40">
+        <v>49.213000000000001</v>
+      </c>
+      <c r="C76" s="40">
+        <v>50.209000000000003</v>
+      </c>
+      <c r="D76" s="40">
+        <v>64.516999999999996</v>
+      </c>
+      <c r="E76" s="40">
+        <v>47.073999999999998</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B77" s="40">
+        <v>11.603</v>
+      </c>
+      <c r="C77" s="40">
+        <v>10.551</v>
+      </c>
+      <c r="D77" s="40">
+        <v>25.032</v>
+      </c>
+      <c r="E77" s="40">
+        <v>9.86</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" s="40" t="s">
+        <v>607</v>
+      </c>
+      <c r="B79" s="40">
+        <v>100.446</v>
+      </c>
+      <c r="C79" s="40">
+        <v>86.465999999999994</v>
+      </c>
+      <c r="D79" s="40">
+        <v>102.36</v>
+      </c>
+      <c r="E79" s="40">
+        <v>82.49</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B80" s="40">
+        <v>13.946999999999999</v>
+      </c>
+      <c r="C80" s="40">
+        <v>5.7649999999999997</v>
+      </c>
+      <c r="D80" s="40">
+        <v>22.632000000000001</v>
+      </c>
+      <c r="E80" s="40">
+        <v>5.4740000000000002</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" s="40" t="s">
+        <v>606</v>
+      </c>
+      <c r="B82" s="40">
+        <v>9.65</v>
+      </c>
+      <c r="C82" s="40">
+        <v>8.5730000000000004</v>
+      </c>
+      <c r="D82" s="40">
+        <v>7.3220000000000001</v>
+      </c>
+      <c r="E82" s="40">
+        <v>8.0679999999999996</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B83" s="40">
+        <v>1.7330000000000001</v>
+      </c>
+      <c r="C83" s="40">
+        <v>1.87</v>
+      </c>
+      <c r="D83" s="40">
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="E83" s="40">
+        <v>1.722</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="40" t="s">
+        <v>605</v>
+      </c>
+      <c r="B85" s="40">
+        <v>159.71</v>
+      </c>
+      <c r="C85" s="40">
+        <v>202.803</v>
+      </c>
+      <c r="D85" s="40">
+        <v>192.38399999999999</v>
+      </c>
+      <c r="E85" s="40">
+        <v>201.977</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B86" s="40">
+        <v>37.518000000000001</v>
+      </c>
+      <c r="C86" s="40">
+        <v>41.94</v>
+      </c>
+      <c r="D86" s="40">
+        <v>33.534999999999997</v>
+      </c>
+      <c r="E86" s="40">
+        <v>38.549999999999997</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" s="40" t="s">
+        <v>604</v>
+      </c>
+      <c r="B88" s="40">
+        <v>214.839</v>
+      </c>
+      <c r="C88" s="40">
+        <v>194.88399999999999</v>
+      </c>
+      <c r="D88" s="40">
+        <v>207.791</v>
+      </c>
+      <c r="E88" s="40">
+        <v>185.21600000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B89" s="40">
+        <v>18.911999999999999</v>
+      </c>
+      <c r="C89" s="40">
+        <v>18.029</v>
+      </c>
+      <c r="D89" s="40">
+        <v>39.662999999999997</v>
+      </c>
+      <c r="E89" s="40">
+        <v>17.535</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" s="40" t="s">
+        <v>603</v>
+      </c>
+      <c r="B91" s="40" t="s">
+        <v>589</v>
+      </c>
+      <c r="C91" s="40">
+        <v>1.0649999999999999</v>
+      </c>
+      <c r="D91" s="40">
+        <v>1.419</v>
+      </c>
+      <c r="E91" s="40">
+        <v>0.94599999999999995</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B92" s="40" t="s">
+        <v>589</v>
+      </c>
+      <c r="C92" s="40">
+        <v>1.018</v>
+      </c>
+      <c r="D92" s="40">
+        <v>1.3740000000000001</v>
+      </c>
+      <c r="E92" s="40">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" s="40" t="s">
+        <v>602</v>
+      </c>
+      <c r="B94" s="40" t="s">
+        <v>589</v>
+      </c>
+      <c r="C94" s="40">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="D94" s="40">
+        <v>0.77600000000000002</v>
+      </c>
+      <c r="E94" s="40">
+        <v>0.96799999999999997</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B95" s="40" t="s">
+        <v>589</v>
+      </c>
+      <c r="C95" s="40">
+        <v>0.307</v>
+      </c>
+      <c r="D95" s="40">
+        <v>0.111</v>
+      </c>
+      <c r="E95" s="40">
+        <v>0.29599999999999999</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" s="40" t="s">
+        <v>601</v>
+      </c>
+      <c r="B97" s="40">
+        <v>18.356999999999999</v>
+      </c>
+      <c r="C97" s="40">
+        <v>18.137</v>
+      </c>
+      <c r="D97" s="40">
+        <v>54.454999999999998</v>
+      </c>
+      <c r="E97" s="40">
+        <v>4.4349999999999996</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B98" s="40">
+        <v>10.608000000000001</v>
+      </c>
+      <c r="C98" s="40">
+        <v>9.0370000000000008</v>
+      </c>
+      <c r="D98" s="40">
+        <v>45.448999999999998</v>
+      </c>
+      <c r="E98" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" s="40" t="s">
+        <v>600</v>
+      </c>
+      <c r="B100" s="40" t="s">
+        <v>589</v>
+      </c>
+      <c r="C100" s="40">
+        <v>0.93700000000000006</v>
+      </c>
+      <c r="D100" s="40">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="E100" s="40">
+        <v>0.93799999999999994</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B101" s="40" t="s">
+        <v>589</v>
+      </c>
+      <c r="C101" s="40">
+        <v>0.6</v>
+      </c>
+      <c r="D101" s="40">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="E101" s="40">
+        <v>0.59399999999999997</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="40" t="s">
+        <v>599</v>
+      </c>
+      <c r="B103" s="40">
+        <v>68.063000000000002</v>
+      </c>
+      <c r="C103" s="40">
+        <v>47.756999999999998</v>
+      </c>
+      <c r="D103" s="40">
+        <v>51.521000000000001</v>
+      </c>
+      <c r="E103" s="40">
+        <v>50.261000000000003</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B104" s="40">
+        <v>16.379000000000001</v>
+      </c>
+      <c r="C104" s="40">
+        <v>3.782</v>
+      </c>
+      <c r="D104" s="40">
+        <v>6.43</v>
+      </c>
+      <c r="E104" s="40">
+        <v>4.0309999999999997</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" s="40" t="s">
+        <v>598</v>
+      </c>
+      <c r="B106" s="40">
+        <v>581.70000000000005</v>
+      </c>
+      <c r="C106" s="40">
+        <v>370.488</v>
+      </c>
+      <c r="D106" s="40">
+        <v>614.149</v>
+      </c>
+      <c r="E106" s="40">
+        <v>488.471</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B107" s="40">
+        <v>453.02</v>
+      </c>
+      <c r="C107" s="40">
+        <v>225.99</v>
+      </c>
+      <c r="D107" s="40">
+        <v>415.928</v>
+      </c>
+      <c r="E107" s="40">
+        <v>266.31200000000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" s="40" t="s">
+        <v>597</v>
+      </c>
+      <c r="B109" s="40">
+        <v>45.62</v>
+      </c>
+      <c r="C109" s="40">
+        <v>0</v>
+      </c>
+      <c r="D109" s="40">
+        <v>0</v>
+      </c>
+      <c r="E109" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B110" s="40">
+        <v>4.2839999999999998</v>
+      </c>
+      <c r="C110" s="40">
+        <v>0</v>
+      </c>
+      <c r="D110" s="40">
+        <v>0</v>
+      </c>
+      <c r="E110" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" s="40" t="s">
+        <v>596</v>
+      </c>
+      <c r="B112" s="40">
+        <v>25.35</v>
+      </c>
+      <c r="C112" s="40">
+        <v>0</v>
+      </c>
+      <c r="D112" s="40">
+        <v>0</v>
+      </c>
+      <c r="E112" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B113" s="40">
+        <v>4.3689999999999998</v>
+      </c>
+      <c r="C113" s="40">
+        <v>0</v>
+      </c>
+      <c r="D113" s="40">
+        <v>0</v>
+      </c>
+      <c r="E113" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" s="40" t="s">
+        <v>595</v>
+      </c>
+      <c r="B115" s="40">
+        <v>10.956</v>
+      </c>
+      <c r="C115" s="40">
+        <v>0</v>
+      </c>
+      <c r="D115" s="40">
+        <v>0</v>
+      </c>
+      <c r="E115" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B116" s="40">
+        <v>3.6349999999999998</v>
+      </c>
+      <c r="C116" s="40">
+        <v>0</v>
+      </c>
+      <c r="D116" s="40">
+        <v>0</v>
+      </c>
+      <c r="E116" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" s="40" t="s">
+        <v>594</v>
+      </c>
+      <c r="B118" s="40">
+        <v>1.1859999999999999</v>
+      </c>
+      <c r="C118" s="40">
+        <v>0</v>
+      </c>
+      <c r="D118" s="40">
+        <v>0</v>
+      </c>
+      <c r="E118" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" s="40" t="s">
+        <v>593</v>
+      </c>
+      <c r="B119" s="40">
+        <v>0.80600000000000005</v>
+      </c>
+      <c r="C119" s="40">
+        <v>0</v>
+      </c>
+      <c r="D119" s="40">
+        <v>0</v>
+      </c>
+      <c r="E119" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" s="41" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" s="40" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" s="40" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" s="40" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" s="40" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" s="40" t="s">
+        <v>591</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4302F27-C534-6F44-8E88-E9ABB33C01B1}">
+  <dimension ref="A1:M128"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="10.83203125" style="67"/>
+    <col min="3" max="3" width="25.83203125" style="67" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="67"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" s="67" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="67" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="67" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="67" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="67" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="67" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="67" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="67" t="s">
+        <v>632</v>
+      </c>
+      <c r="B8" s="67" t="s">
+        <v>631</v>
+      </c>
+      <c r="C8" s="67" t="s">
+        <v>630</v>
+      </c>
+      <c r="D8" s="67" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="67">
+        <v>1</v>
+      </c>
+      <c r="B9" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D9" s="67">
+        <v>98.35</v>
+      </c>
+      <c r="G9" s="75" t="s">
+        <v>628</v>
+      </c>
+      <c r="H9" s="75" t="s">
+        <v>627</v>
+      </c>
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75"/>
+      <c r="L9" s="75"/>
+      <c r="M9" s="75"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="67">
+        <v>2</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C10" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D10" s="67">
+        <v>63.13</v>
+      </c>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75" t="s">
+        <v>619</v>
+      </c>
+      <c r="I10" s="75"/>
+      <c r="J10" s="75"/>
+      <c r="K10" s="75"/>
+      <c r="L10" s="75"/>
+      <c r="M10" s="74" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" s="67">
+        <v>3</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C11" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D11" s="67">
+        <v>77.17</v>
+      </c>
+      <c r="G11" s="73" t="s">
+        <v>625</v>
+      </c>
+      <c r="H11" s="73" t="s">
+        <v>624</v>
+      </c>
+      <c r="I11" s="73" t="s">
+        <v>621</v>
+      </c>
+      <c r="J11" s="73" t="s">
+        <v>618</v>
+      </c>
+      <c r="K11" s="73" t="s">
+        <v>622</v>
+      </c>
+      <c r="L11" s="73" t="s">
+        <v>620</v>
+      </c>
+      <c r="M11" s="72"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="67">
+        <v>4</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C12" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D12" s="67">
+        <v>76.709999999999994</v>
+      </c>
+      <c r="G12" s="71">
+        <v>0</v>
+      </c>
+      <c r="H12" s="67">
+        <v>98.35</v>
+      </c>
+      <c r="I12" s="67">
+        <v>6.53</v>
+      </c>
+      <c r="J12" s="67">
+        <v>6.53</v>
+      </c>
+      <c r="K12" s="67">
+        <v>12.33</v>
+      </c>
+      <c r="L12" s="67">
+        <v>6.53</v>
+      </c>
+      <c r="M12" s="70">
+        <v>26.053999999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="67">
+        <v>5</v>
+      </c>
+      <c r="B13" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C13" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D13" s="67">
+        <v>74.77</v>
+      </c>
+      <c r="G13" s="71">
+        <v>1</v>
+      </c>
+      <c r="H13" s="67">
+        <v>63.13</v>
+      </c>
+      <c r="I13" s="67">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="J13" s="67">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="K13" s="67">
+        <v>11.28</v>
+      </c>
+      <c r="L13" s="67">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="M13" s="70">
+        <v>17.744</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="67">
+        <v>6</v>
+      </c>
+      <c r="B14" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D14" s="67">
+        <v>78.06</v>
+      </c>
+      <c r="G14" s="71">
+        <v>2</v>
+      </c>
+      <c r="H14" s="67">
+        <v>77.17</v>
+      </c>
+      <c r="I14" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="J14" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="K14" s="67">
+        <v>11.2</v>
+      </c>
+      <c r="L14" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="M14" s="70">
+        <v>20.601999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" s="67">
+        <v>7</v>
+      </c>
+      <c r="B15" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D15" s="67">
+        <v>194.51</v>
+      </c>
+      <c r="G15" s="71">
+        <v>3</v>
+      </c>
+      <c r="H15" s="67">
+        <v>76.709999999999994</v>
+      </c>
+      <c r="I15" s="67">
+        <v>5.27</v>
+      </c>
+      <c r="J15" s="67">
+        <v>5.27</v>
+      </c>
+      <c r="K15" s="67">
+        <v>10.06</v>
+      </c>
+      <c r="L15" s="67">
+        <v>5.27</v>
+      </c>
+      <c r="M15" s="70">
+        <v>20.515999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" s="67">
+        <v>8</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C16" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D16" s="67">
+        <v>184.9</v>
+      </c>
+      <c r="G16" s="71">
+        <v>4</v>
+      </c>
+      <c r="H16" s="67">
+        <v>74.77</v>
+      </c>
+      <c r="I16" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="J16" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="K16" s="67">
+        <v>9.3800000000000008</v>
+      </c>
+      <c r="L16" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="M16" s="70">
+        <v>19.757999999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="67">
+        <v>9</v>
+      </c>
+      <c r="B17" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C17" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D17" s="67">
+        <v>164.04</v>
+      </c>
+      <c r="G17" s="71">
+        <v>5</v>
+      </c>
+      <c r="H17" s="67">
+        <v>78.06</v>
+      </c>
+      <c r="I17" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="J17" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="K17" s="67">
+        <v>9.24</v>
+      </c>
+      <c r="L17" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="M17" s="70">
+        <v>20.387999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="67">
+        <v>10</v>
+      </c>
+      <c r="B18" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C18" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D18" s="67">
+        <v>148</v>
+      </c>
+      <c r="G18" s="71">
+        <v>6</v>
+      </c>
+      <c r="H18" s="67">
+        <v>194.51</v>
+      </c>
+      <c r="I18" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="J18" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="K18" s="67">
+        <v>8.32</v>
+      </c>
+      <c r="L18" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="M18" s="70">
+        <v>43.493999999999993</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="67">
+        <v>11</v>
+      </c>
+      <c r="B19" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C19" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D19" s="67">
+        <v>152.54</v>
+      </c>
+      <c r="G19" s="71">
+        <v>7</v>
+      </c>
+      <c r="H19" s="67">
+        <v>184.9</v>
+      </c>
+      <c r="I19" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="J19" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="K19" s="67">
+        <v>7.63</v>
+      </c>
+      <c r="L19" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="M19" s="70">
+        <v>41.338000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="67">
+        <v>12</v>
+      </c>
+      <c r="B20" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C20" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D20" s="67">
+        <v>141.52000000000001</v>
+      </c>
+      <c r="G20" s="71">
+        <v>8</v>
+      </c>
+      <c r="H20" s="67">
+        <v>164.04</v>
+      </c>
+      <c r="I20" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="J20" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="K20" s="67">
+        <v>6.84</v>
+      </c>
+      <c r="L20" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="M20" s="70">
+        <v>37.007999999999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="67">
+        <v>13</v>
+      </c>
+      <c r="B21" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C21" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D21" s="67">
+        <v>159.59</v>
+      </c>
+      <c r="G21" s="71">
+        <v>9</v>
+      </c>
+      <c r="H21" s="67">
+        <v>148</v>
+      </c>
+      <c r="I21" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="J21" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="K21" s="67">
+        <v>6.84</v>
+      </c>
+      <c r="L21" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="M21" s="70">
+        <v>33.799999999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="67">
+        <v>14</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C22" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D22" s="67">
+        <v>177.9</v>
+      </c>
+      <c r="G22" s="71">
+        <v>10</v>
+      </c>
+      <c r="H22" s="67">
+        <v>152.54</v>
+      </c>
+      <c r="I22" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="J22" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="K22" s="67">
+        <v>6.84</v>
+      </c>
+      <c r="L22" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="M22" s="70">
+        <v>34.707999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" s="67">
+        <v>15</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C23" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D23" s="67">
+        <v>194.31</v>
+      </c>
+      <c r="G23" s="71">
+        <v>11</v>
+      </c>
+      <c r="H23" s="67">
+        <v>141.52000000000001</v>
+      </c>
+      <c r="I23" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="J23" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="K23" s="67">
+        <v>7.39</v>
+      </c>
+      <c r="L23" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="M23" s="70">
+        <v>32.613999999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" s="67">
+        <v>16</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C24" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D24" s="67">
+        <v>104.1</v>
+      </c>
+      <c r="G24" s="71">
+        <v>12</v>
+      </c>
+      <c r="H24" s="67">
+        <v>159.59</v>
+      </c>
+      <c r="I24" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="J24" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="K24" s="67">
+        <v>7.39</v>
+      </c>
+      <c r="L24" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="M24" s="70">
+        <v>36.227999999999994</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" s="67">
+        <v>17</v>
+      </c>
+      <c r="B25" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C25" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D25" s="67">
+        <v>234.43</v>
+      </c>
+      <c r="G25" s="71">
+        <v>13</v>
+      </c>
+      <c r="H25" s="67">
+        <v>177.9</v>
+      </c>
+      <c r="I25" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="J25" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="K25" s="67">
+        <v>8.17</v>
+      </c>
+      <c r="L25" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="M25" s="70">
+        <v>40.141999999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" s="67">
+        <v>18</v>
+      </c>
+      <c r="B26" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C26" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D26" s="67">
+        <v>59.69</v>
+      </c>
+      <c r="G26" s="71">
+        <v>14</v>
+      </c>
+      <c r="H26" s="67">
+        <v>194.31</v>
+      </c>
+      <c r="I26" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="J26" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="K26" s="67">
+        <v>7.63</v>
+      </c>
+      <c r="L26" s="67">
+        <v>4.72</v>
+      </c>
+      <c r="M26" s="70">
+        <v>43.22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A27" s="67">
+        <v>19</v>
+      </c>
+      <c r="B27" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C27" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D27" s="67">
+        <v>84.42</v>
+      </c>
+      <c r="G27" s="71">
+        <v>15</v>
+      </c>
+      <c r="H27" s="67">
+        <v>104.1</v>
+      </c>
+      <c r="I27" s="67">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="J27" s="67">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="K27" s="67">
+        <v>8.06</v>
+      </c>
+      <c r="L27" s="67">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="M27" s="70">
+        <v>25.293999999999997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A28" s="67">
+        <v>20</v>
+      </c>
+      <c r="B28" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D28" s="67">
+        <v>195.51</v>
+      </c>
+      <c r="G28" s="71">
+        <v>16</v>
+      </c>
+      <c r="H28" s="67">
+        <v>234.43</v>
+      </c>
+      <c r="I28" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="J28" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="K28" s="67">
+        <v>9.11</v>
+      </c>
+      <c r="L28" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="M28" s="70">
+        <v>51.636000000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A29" s="67">
+        <v>21</v>
+      </c>
+      <c r="B29" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C29" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D29" s="67">
+        <v>206.23</v>
+      </c>
+      <c r="G29" s="71">
+        <v>17</v>
+      </c>
+      <c r="H29" s="67">
+        <v>59.69</v>
+      </c>
+      <c r="I29" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="J29" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="K29" s="67">
+        <v>9.81</v>
+      </c>
+      <c r="L29" s="67">
+        <v>4.88</v>
+      </c>
+      <c r="M29" s="70">
+        <v>16.827999999999996</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A30" s="67">
+        <v>22</v>
+      </c>
+      <c r="B30" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C30" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D30" s="67">
+        <v>146.79</v>
+      </c>
+      <c r="G30" s="71">
+        <v>18</v>
+      </c>
+      <c r="H30" s="67">
+        <v>84.42</v>
+      </c>
+      <c r="I30" s="67">
+        <v>7.21</v>
+      </c>
+      <c r="J30" s="67">
+        <v>7.21</v>
+      </c>
+      <c r="K30" s="67">
+        <v>15.36</v>
+      </c>
+      <c r="L30" s="67">
+        <v>7.21</v>
+      </c>
+      <c r="M30" s="70">
+        <v>24.281999999999996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A31" s="67">
+        <v>23</v>
+      </c>
+      <c r="B31" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C31" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D31" s="67">
+        <v>170.45</v>
+      </c>
+      <c r="G31" s="71">
+        <v>19</v>
+      </c>
+      <c r="H31" s="67">
+        <v>195.51</v>
+      </c>
+      <c r="I31" s="67">
+        <v>10.68</v>
+      </c>
+      <c r="J31" s="67">
+        <v>10.68</v>
+      </c>
+      <c r="K31" s="67">
+        <v>66.28</v>
+      </c>
+      <c r="L31" s="67">
+        <v>10.68</v>
+      </c>
+      <c r="M31" s="70">
+        <v>58.765999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A32" s="67">
+        <v>24</v>
+      </c>
+      <c r="B32" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C32" s="67" t="s">
+        <v>624</v>
+      </c>
+      <c r="D32" s="67">
+        <v>74.12</v>
+      </c>
+      <c r="G32" s="71">
+        <v>20</v>
+      </c>
+      <c r="H32" s="67">
+        <v>206.23</v>
+      </c>
+      <c r="I32" s="67">
+        <v>11.28</v>
+      </c>
+      <c r="J32" s="67">
+        <v>11.28</v>
+      </c>
+      <c r="K32" s="67">
+        <v>67.36</v>
+      </c>
+      <c r="L32" s="67">
+        <v>11.28</v>
+      </c>
+      <c r="M32" s="70">
+        <v>61.48599999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33" s="67">
+        <v>1</v>
+      </c>
+      <c r="B33" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C33" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D33" s="67">
+        <v>12.33</v>
+      </c>
+      <c r="G33" s="71">
+        <v>21</v>
+      </c>
+      <c r="H33" s="67">
+        <v>146.79</v>
+      </c>
+      <c r="I33" s="67">
+        <v>7.92</v>
+      </c>
+      <c r="J33" s="67">
+        <v>7.92</v>
+      </c>
+      <c r="K33" s="67">
+        <v>52.99</v>
+      </c>
+      <c r="L33" s="67">
+        <v>7.92</v>
+      </c>
+      <c r="M33" s="70">
+        <v>44.707999999999991</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" s="67">
+        <v>2</v>
+      </c>
+      <c r="B34" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C34" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D34" s="67">
+        <v>11.28</v>
+      </c>
+      <c r="G34" s="71">
+        <v>22</v>
+      </c>
+      <c r="H34" s="67">
+        <v>170.45</v>
+      </c>
+      <c r="I34" s="67">
+        <v>8.5</v>
+      </c>
+      <c r="J34" s="67">
+        <v>8.5</v>
+      </c>
+      <c r="K34" s="67">
+        <v>51.95</v>
+      </c>
+      <c r="L34" s="67">
+        <v>8.5</v>
+      </c>
+      <c r="M34" s="70">
+        <v>49.58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A35" s="67">
+        <v>3</v>
+      </c>
+      <c r="B35" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C35" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D35" s="67">
+        <v>11.2</v>
+      </c>
+      <c r="G35" s="71">
+        <v>23</v>
+      </c>
+      <c r="H35" s="67">
+        <v>74.12</v>
+      </c>
+      <c r="I35" s="67">
+        <v>7.2</v>
+      </c>
+      <c r="J35" s="67">
+        <v>7.2</v>
+      </c>
+      <c r="K35" s="67">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="L35" s="67">
+        <v>7.2</v>
+      </c>
+      <c r="M35" s="70">
+        <v>22.724000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A36" s="67">
+        <v>4</v>
+      </c>
+      <c r="B36" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C36" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D36" s="67">
+        <v>10.06</v>
+      </c>
+      <c r="G36" s="69" t="s">
+        <v>623</v>
+      </c>
+      <c r="H36" s="68">
+        <v>135.88499999999996</v>
+      </c>
+      <c r="I36" s="68">
+        <v>5.888749999999999</v>
+      </c>
+      <c r="J36" s="68">
+        <v>5.888749999999999</v>
+      </c>
+      <c r="K36" s="68">
+        <v>17.89</v>
+      </c>
+      <c r="L36" s="68">
+        <v>5.888749999999999</v>
+      </c>
+      <c r="M36" s="68">
+        <v>34.288249999999991</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A37" s="67">
+        <v>5</v>
+      </c>
+      <c r="B37" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C37" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D37" s="67">
+        <v>9.3800000000000008</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A38" s="67">
+        <v>6</v>
+      </c>
+      <c r="B38" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C38" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D38" s="67">
+        <v>9.24</v>
+      </c>
+      <c r="H38" s="67">
+        <f>MEDIAN(H12:H35)</f>
+        <v>147.39499999999998</v>
+      </c>
+      <c r="I38" s="67" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A39" s="67">
+        <v>7</v>
+      </c>
+      <c r="B39" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C39" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D39" s="67">
+        <v>8.32</v>
+      </c>
+      <c r="H39" s="67">
+        <f>H38/20</f>
+        <v>7.3697499999999989</v>
+      </c>
+      <c r="I39" s="67" t="s">
+        <v>642</v>
+      </c>
+      <c r="K39" s="67">
+        <v>0.75350342301658668</v>
+      </c>
+      <c r="L39" s="67" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A40" s="67">
+        <v>8</v>
+      </c>
+      <c r="B40" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C40" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D40" s="67">
+        <v>7.63</v>
+      </c>
+      <c r="H40" s="67">
+        <f>H39*K39</f>
+        <v>5.5531318517764889</v>
+      </c>
+      <c r="I40" s="67" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A41" s="67">
+        <v>9</v>
+      </c>
+      <c r="B41" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C41" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D41" s="67">
+        <v>6.84</v>
+      </c>
+      <c r="H41" s="67">
+        <f>H40*24*365</f>
+        <v>48645.435021562043</v>
+      </c>
+      <c r="I41" s="67" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A42" s="67">
+        <v>10</v>
+      </c>
+      <c r="B42" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C42" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D42" s="67">
+        <v>6.84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A43" s="67">
+        <v>11</v>
+      </c>
+      <c r="B43" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C43" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D43" s="67">
+        <v>6.84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A44" s="67">
+        <v>12</v>
+      </c>
+      <c r="B44" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C44" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D44" s="67">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A45" s="67">
+        <v>13</v>
+      </c>
+      <c r="B45" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C45" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D45" s="67">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A46" s="67">
+        <v>14</v>
+      </c>
+      <c r="B46" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C46" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D46" s="67">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A47" s="67">
+        <v>15</v>
+      </c>
+      <c r="B47" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C47" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D47" s="67">
+        <v>7.63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A48" s="67">
+        <v>16</v>
+      </c>
+      <c r="B48" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C48" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D48" s="67">
+        <v>8.06</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="67">
+        <v>17</v>
+      </c>
+      <c r="B49" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C49" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D49" s="67">
+        <v>9.11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="67">
+        <v>18</v>
+      </c>
+      <c r="B50" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C50" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D50" s="67">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="67">
+        <v>19</v>
+      </c>
+      <c r="B51" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C51" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D51" s="67">
+        <v>15.36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="67">
+        <v>20</v>
+      </c>
+      <c r="B52" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C52" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D52" s="67">
+        <v>66.28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="67">
+        <v>21</v>
+      </c>
+      <c r="B53" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C53" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D53" s="67">
+        <v>67.36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="67">
+        <v>22</v>
+      </c>
+      <c r="B54" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C54" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D54" s="67">
+        <v>52.99</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="67">
+        <v>23</v>
+      </c>
+      <c r="B55" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C55" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D55" s="67">
+        <v>51.95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="67">
+        <v>24</v>
+      </c>
+      <c r="B56" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C56" s="67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D56" s="67">
+        <v>17.899999999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="67">
+        <v>1</v>
+      </c>
+      <c r="B57" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C57" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D57" s="67">
+        <v>6.53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="67">
+        <v>2</v>
+      </c>
+      <c r="B58" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C58" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D58" s="67">
+        <v>4.7699999999999996</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="67">
+        <v>3</v>
+      </c>
+      <c r="B59" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C59" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D59" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="67">
+        <v>4</v>
+      </c>
+      <c r="B60" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C60" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D60" s="67">
+        <v>5.27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="67">
+        <v>5</v>
+      </c>
+      <c r="B61" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C61" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D61" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="67">
+        <v>6</v>
+      </c>
+      <c r="B62" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C62" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D62" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="67">
+        <v>7</v>
+      </c>
+      <c r="B63" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C63" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D63" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="67">
+        <v>8</v>
+      </c>
+      <c r="B64" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C64" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D64" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="67">
+        <v>9</v>
+      </c>
+      <c r="B65" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C65" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D65" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="67">
+        <v>10</v>
+      </c>
+      <c r="B66" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C66" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D66" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="67">
+        <v>11</v>
+      </c>
+      <c r="B67" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C67" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D67" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="67">
+        <v>12</v>
+      </c>
+      <c r="B68" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C68" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D68" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="67">
+        <v>13</v>
+      </c>
+      <c r="B69" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C69" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D69" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="67">
+        <v>14</v>
+      </c>
+      <c r="B70" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C70" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D70" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="67">
+        <v>15</v>
+      </c>
+      <c r="B71" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C71" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D71" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="67">
+        <v>16</v>
+      </c>
+      <c r="B72" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C72" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D72" s="67">
+        <v>4.7699999999999996</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="67">
+        <v>17</v>
+      </c>
+      <c r="B73" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C73" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D73" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="67">
+        <v>18</v>
+      </c>
+      <c r="B74" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C74" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D74" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="67">
+        <v>19</v>
+      </c>
+      <c r="B75" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C75" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D75" s="67">
+        <v>7.21</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="67">
+        <v>20</v>
+      </c>
+      <c r="B76" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C76" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D76" s="67">
+        <v>10.68</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="67">
+        <v>21</v>
+      </c>
+      <c r="B77" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C77" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D77" s="67">
+        <v>11.28</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="67">
+        <v>22</v>
+      </c>
+      <c r="B78" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C78" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D78" s="67">
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="67">
+        <v>23</v>
+      </c>
+      <c r="B79" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C79" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D79" s="67">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" s="67">
+        <v>24</v>
+      </c>
+      <c r="B80" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C80" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="D80" s="67">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" s="67">
+        <v>1</v>
+      </c>
+      <c r="B81" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C81" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D81" s="67">
+        <v>6.53</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" s="67">
+        <v>2</v>
+      </c>
+      <c r="B82" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C82" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D82" s="67">
+        <v>4.7699999999999996</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="67">
+        <v>3</v>
+      </c>
+      <c r="B83" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C83" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D83" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="67">
+        <v>4</v>
+      </c>
+      <c r="B84" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C84" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D84" s="67">
+        <v>5.27</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="67">
+        <v>5</v>
+      </c>
+      <c r="B85" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C85" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D85" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="67">
+        <v>6</v>
+      </c>
+      <c r="B86" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C86" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D86" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" s="67">
+        <v>7</v>
+      </c>
+      <c r="B87" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C87" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D87" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" s="67">
+        <v>8</v>
+      </c>
+      <c r="B88" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C88" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D88" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="67">
+        <v>9</v>
+      </c>
+      <c r="B89" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C89" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D89" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" s="67">
+        <v>10</v>
+      </c>
+      <c r="B90" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C90" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D90" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" s="67">
+        <v>11</v>
+      </c>
+      <c r="B91" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C91" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D91" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="67">
+        <v>12</v>
+      </c>
+      <c r="B92" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C92" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D92" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" s="67">
+        <v>13</v>
+      </c>
+      <c r="B93" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C93" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D93" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" s="67">
+        <v>14</v>
+      </c>
+      <c r="B94" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C94" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D94" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" s="67">
+        <v>15</v>
+      </c>
+      <c r="B95" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C95" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D95" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="67">
+        <v>16</v>
+      </c>
+      <c r="B96" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C96" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D96" s="67">
+        <v>4.7699999999999996</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97" s="67">
+        <v>17</v>
+      </c>
+      <c r="B97" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C97" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D97" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" s="67">
+        <v>18</v>
+      </c>
+      <c r="B98" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C98" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D98" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" s="67">
+        <v>19</v>
+      </c>
+      <c r="B99" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C99" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D99" s="67">
+        <v>7.21</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" s="67">
+        <v>20</v>
+      </c>
+      <c r="B100" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C100" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D100" s="67">
+        <v>10.68</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101" s="67">
+        <v>21</v>
+      </c>
+      <c r="B101" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C101" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D101" s="67">
+        <v>11.28</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" s="67">
+        <v>22</v>
+      </c>
+      <c r="B102" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C102" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D102" s="67">
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" s="67">
+        <v>23</v>
+      </c>
+      <c r="B103" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C103" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D103" s="67">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104" s="67">
+        <v>24</v>
+      </c>
+      <c r="B104" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C104" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="D104" s="67">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105" s="67">
+        <v>1</v>
+      </c>
+      <c r="B105" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C105" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D105" s="67">
+        <v>6.53</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106" s="67">
+        <v>2</v>
+      </c>
+      <c r="B106" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C106" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D106" s="67">
+        <v>4.7699999999999996</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107" s="67">
+        <v>3</v>
+      </c>
+      <c r="B107" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C107" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D107" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108" s="67">
+        <v>4</v>
+      </c>
+      <c r="B108" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C108" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D108" s="67">
+        <v>5.27</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A109" s="67">
+        <v>5</v>
+      </c>
+      <c r="B109" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C109" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D109" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110" s="67">
+        <v>6</v>
+      </c>
+      <c r="B110" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C110" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D110" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A111" s="67">
+        <v>7</v>
+      </c>
+      <c r="B111" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C111" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D111" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A112" s="67">
+        <v>8</v>
+      </c>
+      <c r="B112" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C112" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D112" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A113" s="67">
+        <v>9</v>
+      </c>
+      <c r="B113" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C113" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D113" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A114" s="67">
+        <v>10</v>
+      </c>
+      <c r="B114" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C114" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D114" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A115" s="67">
+        <v>11</v>
+      </c>
+      <c r="B115" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C115" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D115" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A116" s="67">
+        <v>12</v>
+      </c>
+      <c r="B116" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C116" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D116" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A117" s="67">
+        <v>13</v>
+      </c>
+      <c r="B117" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C117" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D117" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A118" s="67">
+        <v>14</v>
+      </c>
+      <c r="B118" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C118" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D118" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A119" s="67">
+        <v>15</v>
+      </c>
+      <c r="B119" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C119" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D119" s="67">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A120" s="67">
+        <v>16</v>
+      </c>
+      <c r="B120" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C120" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D120" s="67">
+        <v>4.7699999999999996</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A121" s="67">
+        <v>17</v>
+      </c>
+      <c r="B121" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C121" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D121" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A122" s="67">
+        <v>18</v>
+      </c>
+      <c r="B122" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C122" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D122" s="67">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A123" s="67">
+        <v>19</v>
+      </c>
+      <c r="B123" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C123" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D123" s="67">
+        <v>7.21</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A124" s="67">
+        <v>20</v>
+      </c>
+      <c r="B124" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C124" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D124" s="67">
+        <v>10.68</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125" s="67">
+        <v>21</v>
+      </c>
+      <c r="B125" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C125" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D125" s="67">
+        <v>11.28</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A126" s="67">
+        <v>22</v>
+      </c>
+      <c r="B126" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C126" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D126" s="67">
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A127" s="67">
+        <v>23</v>
+      </c>
+      <c r="B127" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C127" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D127" s="67">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A128" s="67">
+        <v>24</v>
+      </c>
+      <c r="B128" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="C128" s="67" t="s">
+        <v>618</v>
+      </c>
+      <c r="D128" s="67">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.1640625" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1">
+    <row r="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>538</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="9"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>539</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="9"/>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>540</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="9"/>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B6" s="10" t="s">
         <v>541</v>
       </c>
@@ -57498,84 +61460,84 @@
         <v>542</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>543</v>
       </c>
-      <c r="B7" s="11" cm="1">
-        <f t="array" ref="B7">MEDIAN(IF('Demand Response_States'!F:F&lt;&gt;0,'Demand Response_States'!F:F))</f>
-        <v>41502.8901734104</v>
+      <c r="B7" s="11">
+        <f>'PreciosServiciosConexos SIN MTR'!$H$41</f>
+        <v>48645.435021562043</v>
       </c>
       <c r="C7" s="9">
-        <f>SUM('Demand Response_States'!T:T)/SUM('Demand Response_States'!X:X)</f>
-        <v>0.27639423854992745</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <f>'Mexico_id-7'!B29/'Mexico_id-7'!$B$20</f>
+        <v>0.63854750249186143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>544</v>
       </c>
-      <c r="B8" s="11" cm="1">
-        <f t="array" ref="B8">MEDIAN(IF('Demand Response_States'!G:G&lt;&gt;0,'Demand Response_States'!G:G))</f>
-        <v>28125</v>
+      <c r="B8" s="11">
+        <f>'PreciosServiciosConexos SIN MTR'!H41*(AVERAGE('Demand Response_States'!G:G)/AVERAGE('Demand Response_States'!F:F))</f>
+        <v>13231.046306460883</v>
       </c>
       <c r="C8" s="9">
-        <f>SUM('Demand Response_States'!U:U)/SUM('Demand Response_States'!X:X)</f>
-        <v>0.22725360090629559</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <f>('Mexico_id-7'!B37+'Mexico_id-7'!B40)/'Mexico_id-7'!B20</f>
+        <v>0.16965035377068979</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>545</v>
       </c>
-      <c r="B9" s="11" cm="1">
-        <f t="array" ref="B9">MEDIAN(IF('Demand Response_States'!H:H&lt;&gt;0,'Demand Response_States'!H:H))</f>
-        <v>24407.32600732601</v>
+      <c r="B9" s="11">
+        <f>'PreciosServiciosConexos SIN MTR'!H41*(AVERAGE('Demand Response_States'!H:H)/AVERAGE('Demand Response_States'!F:F))</f>
+        <v>45129.321443857662</v>
       </c>
       <c r="C9" s="9">
-        <f>SUM('Demand Response_States'!V:V)/SUM('Demand Response_States'!X:X)</f>
-        <v>0.49636510762259262</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <f>'Mexico_id-7'!B59/'Mexico_id-7'!B20</f>
+        <v>0.19180214373744864</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>543</v>
       </c>
       <c r="B16" s="11">
         <f>B7</f>
-        <v>41502.8901734104</v>
+        <v>48645.435021562043</v>
       </c>
       <c r="C16" s="12">
         <f>C7</f>
-        <v>0.27639423854992745</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>0.63854750249186143</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>549</v>
       </c>
       <c r="B17" s="11">
         <f>(B8*C8+B9*C9)/SUM(C8:C9)</f>
-        <v>25574.867409825722</v>
+        <v>30157.634433693023</v>
       </c>
       <c r="C17" s="12">
         <f>SUM(C8:C9)</f>
-        <v>0.72361870852888821</v>
+        <v>0.36145249750813846</v>
       </c>
     </row>
   </sheetData>
@@ -57584,20 +61546,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="1" max="1" width="36.5" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="39" t="s">
         <v>550</v>
       </c>
@@ -57605,37 +61566,34 @@
         <v>551</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>552</v>
       </c>
       <c r="B2" s="11">
         <f>Calculations!B17*About!$A$34</f>
-        <v>23383.101272803659</v>
-      </c>
-      <c r="E2" s="11"/>
-    </row>
-    <row r="3" spans="1:5">
+        <v>27573.12516272553</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>553</v>
       </c>
       <c r="B3" s="11">
         <f>Calculations!B17*About!$A$34</f>
-        <v>23383.101272803659</v>
-      </c>
-      <c r="E3" s="11"/>
-    </row>
-    <row r="4" spans="1:5">
+        <v>27573.12516272553</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>554</v>
       </c>
       <c r="B4" s="11">
         <f>Calculations!B16*About!$A$34</f>
-        <v>37946.092485549132</v>
-      </c>
-      <c r="E4" s="11"/>
-    </row>
-    <row r="5" spans="1:5">
+        <v>44476.521240214177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>555</v>
       </c>
@@ -57649,18 +61607,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" customWidth="1"/>
+    <col min="1" max="1" width="36.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="39" t="s">
         <v>556</v>
       </c>
@@ -57668,7 +61626,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>552</v>
       </c>
@@ -57676,25 +61634,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>553</v>
       </c>
       <c r="B3" s="13">
         <f>Calculations!C17</f>
-        <v>0.72361870852888821</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>0.36145249750813846</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>554</v>
       </c>
       <c r="B4" s="13">
         <f>Calculations!C16</f>
-        <v>0.27639423854992745</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>0.63854750249186143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>555</v>
       </c>
@@ -57708,15 +61666,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
     <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
@@ -57860,20 +61809,52 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8DFD345-372D-4CFA-8DD6-F56D3BAD6B42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68CD9C2B-CCA3-434C-A139-F8D4F9C88BBA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5680998-D924-497E-86B3-E1417B3423D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6CA46E6-84A2-4683-9B0A-9E8BB2731A80}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6CA46E6-84A2-4683-9B0A-9E8BB2731A80}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8DFD345-372D-4CFA-8DD6-F56D3BAD6B42}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>